--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,180 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>CONMEBOL Copa Libertadores</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Mexican Liga MX</t>
+  </si>
+  <si>
+    <t>UAE Arabian Gulf League</t>
+  </si>
+  <si>
+    <t>Latvian Virsliga</t>
+  </si>
+  <si>
+    <t>Armenian Premier League</t>
+  </si>
+  <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
+    <t>Serbian Super League</t>
+  </si>
+  <si>
+    <t>Dutch Eredivisie</t>
+  </si>
+  <si>
+    <t>English Sky Bet Championship</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>03:05:00</t>
+  </si>
+  <si>
+    <t>13:40:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:25:00</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Independiente (Ecu)</t>
+  </si>
+  <si>
+    <t>Millonarios</t>
+  </si>
+  <si>
+    <t>Pumas UNAM</t>
+  </si>
+  <si>
+    <t>Al-Khaleej Khor Fakkan</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>Ararat Armenia</t>
+  </si>
+  <si>
+    <t>FK Riga</t>
+  </si>
+  <si>
+    <t>Al-Quadisiya (KSA)</t>
+  </si>
+  <si>
+    <t>Al Faisaly ( KSA )</t>
+  </si>
+  <si>
+    <t>Al Rayyan</t>
+  </si>
+  <si>
+    <t>Al Wahda (Abu Dhabi)</t>
+  </si>
+  <si>
+    <t>Zeleznicar Pancevo</t>
+  </si>
+  <si>
+    <t>AZ Alkmaar</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>West Ham</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>Deportivo Cali</t>
+  </si>
+  <si>
+    <t>Leon</t>
+  </si>
+  <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
+    <t>Liepajas Metalurgs</t>
+  </si>
+  <si>
+    <t>FC Syunik</t>
+  </si>
+  <si>
+    <t>FK Auda</t>
+  </si>
+  <si>
+    <t>Al-Ettifaq</t>
+  </si>
+  <si>
+    <t>Al-Ittihad</t>
+  </si>
+  <si>
+    <t>Al Ahli (QAT)</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
+  </si>
+  <si>
+    <t>Macva Sabac</t>
+  </si>
+  <si>
+    <t>Willem II</t>
+  </si>
+  <si>
+    <t>Al-Hazm (KSA)</t>
+  </si>
+  <si>
+    <t>Wrexham</t>
+  </si>
+  <si>
+    <t>2026-09-09 02:17:26</t>
   </si>
 </sst>
 </file>
@@ -585,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1002,3878 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2">
+        <v>1.19</v>
+      </c>
+      <c r="G2">
+        <v>1.22</v>
+      </c>
+      <c r="H2">
+        <v>14</v>
+      </c>
+      <c r="I2">
+        <v>24</v>
+      </c>
+      <c r="J2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <v>1.25</v>
+      </c>
+      <c r="M2">
+        <v>1.02</v>
+      </c>
+      <c r="N2">
+        <v>5.8</v>
+      </c>
+      <c r="O2">
+        <v>1.17</v>
+      </c>
+      <c r="P2">
+        <v>2.72</v>
+      </c>
+      <c r="Q2">
+        <v>1.49</v>
+      </c>
+      <c r="R2">
+        <v>1.69</v>
+      </c>
+      <c r="S2">
+        <v>2.24</v>
+      </c>
+      <c r="T2">
+        <v>2.38</v>
+      </c>
+      <c r="U2">
+        <v>1.6</v>
+      </c>
+      <c r="V2">
+        <v>1.05</v>
+      </c>
+      <c r="W2">
+        <v>5.4</v>
+      </c>
+      <c r="X2">
+        <v>40</v>
+      </c>
+      <c r="Y2">
+        <v>60</v>
+      </c>
+      <c r="Z2">
+        <v>230</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>13.5</v>
+      </c>
+      <c r="AC2">
+        <v>21</v>
+      </c>
+      <c r="AD2">
+        <v>75</v>
+      </c>
+      <c r="AE2">
+        <v>430</v>
+      </c>
+      <c r="AF2">
+        <v>8.4</v>
+      </c>
+      <c r="AG2">
+        <v>16.5</v>
+      </c>
+      <c r="AH2">
+        <v>60</v>
+      </c>
+      <c r="AI2">
+        <v>290</v>
+      </c>
+      <c r="AJ2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK2">
+        <v>18.5</v>
+      </c>
+      <c r="AL2">
+        <v>65</v>
+      </c>
+      <c r="AM2">
+        <v>340</v>
+      </c>
+      <c r="AN2">
+        <v>3.7</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>5.3</v>
+      </c>
+      <c r="AQ2">
+        <v>5.7</v>
+      </c>
+      <c r="AR2">
+        <v>6.2</v>
+      </c>
+      <c r="AS2">
+        <v>6.4</v>
+      </c>
+      <c r="AT2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU2">
+        <v>17.5</v>
+      </c>
+      <c r="AV2">
+        <v>5.8</v>
+      </c>
+      <c r="AW2">
+        <v>6.2</v>
+      </c>
+      <c r="AX2">
+        <v>7</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>5.7</v>
+      </c>
+      <c r="BA2">
+        <v>6.2</v>
+      </c>
+      <c r="BB2">
+        <v>7.2</v>
+      </c>
+      <c r="BC2">
+        <v>13</v>
+      </c>
+      <c r="BD2">
+        <v>5.8</v>
+      </c>
+      <c r="BE2">
+        <v>6.2</v>
+      </c>
+      <c r="BF2">
+        <v>3.15</v>
+      </c>
+      <c r="BG2">
+        <v>6.2</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.28</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.28</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.28</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.28</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.28</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.28</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.28</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.28</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.28</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3">
+        <v>2.68</v>
+      </c>
+      <c r="G3">
+        <v>2.86</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3.15</v>
+      </c>
+      <c r="J3">
+        <v>3.1</v>
+      </c>
+      <c r="K3">
+        <v>3.3</v>
+      </c>
+      <c r="L3">
+        <v>1.45</v>
+      </c>
+      <c r="M3">
+        <v>1.11</v>
+      </c>
+      <c r="N3">
+        <v>2.98</v>
+      </c>
+      <c r="O3">
+        <v>1.45</v>
+      </c>
+      <c r="P3">
+        <v>1.65</v>
+      </c>
+      <c r="Q3">
+        <v>2.34</v>
+      </c>
+      <c r="R3">
+        <v>1.24</v>
+      </c>
+      <c r="S3">
+        <v>4.4</v>
+      </c>
+      <c r="T3">
+        <v>1.95</v>
+      </c>
+      <c r="U3">
+        <v>1.95</v>
+      </c>
+      <c r="V3">
+        <v>1.46</v>
+      </c>
+      <c r="W3">
+        <v>1.53</v>
+      </c>
+      <c r="X3">
+        <v>12.5</v>
+      </c>
+      <c r="Y3">
+        <v>10.5</v>
+      </c>
+      <c r="Z3">
+        <v>24</v>
+      </c>
+      <c r="AA3">
+        <v>65</v>
+      </c>
+      <c r="AB3">
+        <v>11</v>
+      </c>
+      <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>17</v>
+      </c>
+      <c r="AE3">
+        <v>50</v>
+      </c>
+      <c r="AF3">
+        <v>17.5</v>
+      </c>
+      <c r="AG3">
+        <v>13</v>
+      </c>
+      <c r="AH3">
+        <v>20</v>
+      </c>
+      <c r="AI3">
+        <v>75</v>
+      </c>
+      <c r="AJ3">
+        <v>55</v>
+      </c>
+      <c r="AK3">
+        <v>36</v>
+      </c>
+      <c r="AL3">
+        <v>65</v>
+      </c>
+      <c r="AM3">
+        <v>160</v>
+      </c>
+      <c r="AN3">
+        <v>42</v>
+      </c>
+      <c r="AO3">
+        <v>55</v>
+      </c>
+      <c r="AP3">
+        <v>9</v>
+      </c>
+      <c r="AQ3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR3">
+        <v>17</v>
+      </c>
+      <c r="AS3">
+        <v>6</v>
+      </c>
+      <c r="AT3">
+        <v>8</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
+        <v>12</v>
+      </c>
+      <c r="AW3">
+        <v>32</v>
+      </c>
+      <c r="AX3">
+        <v>14</v>
+      </c>
+      <c r="AY3">
+        <v>11</v>
+      </c>
+      <c r="AZ3">
+        <v>17</v>
+      </c>
+      <c r="BA3">
+        <v>6</v>
+      </c>
+      <c r="BB3">
+        <v>30</v>
+      </c>
+      <c r="BC3">
+        <v>5.6</v>
+      </c>
+      <c r="BD3">
+        <v>6</v>
+      </c>
+      <c r="BE3">
+        <v>6.4</v>
+      </c>
+      <c r="BF3">
+        <v>5.8</v>
+      </c>
+      <c r="BG3">
+        <v>36</v>
+      </c>
+      <c r="BH3">
+        <v>3.35</v>
+      </c>
+      <c r="BI3">
+        <v>2.38</v>
+      </c>
+      <c r="BJ3">
+        <v>12.5</v>
+      </c>
+      <c r="BK3">
+        <v>3.55</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>4.9</v>
+      </c>
+      <c r="BN3">
+        <v>6.6</v>
+      </c>
+      <c r="BO3">
+        <v>5</v>
+      </c>
+      <c r="BP3">
+        <v>29</v>
+      </c>
+      <c r="BQ3">
+        <v>4.2</v>
+      </c>
+      <c r="BR3">
+        <v>50</v>
+      </c>
+      <c r="BS3">
+        <v>4.5</v>
+      </c>
+      <c r="BT3">
+        <v>7</v>
+      </c>
+      <c r="BU3">
+        <v>5.2</v>
+      </c>
+      <c r="BV3">
+        <v>32</v>
+      </c>
+      <c r="BW3">
+        <v>4.3</v>
+      </c>
+      <c r="BX3">
+        <v>55</v>
+      </c>
+      <c r="BY3">
+        <v>4.6</v>
+      </c>
+      <c r="BZ3">
+        <v>50</v>
+      </c>
+      <c r="CA3">
+        <v>4.5</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4">
+        <v>1.58</v>
+      </c>
+      <c r="G4">
+        <v>1.88</v>
+      </c>
+      <c r="H4">
+        <v>4.5</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>1.1</v>
+      </c>
+      <c r="K4">
+        <v>950</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>2.68</v>
+      </c>
+      <c r="O4">
+        <v>1.36</v>
+      </c>
+      <c r="P4">
+        <v>1.6</v>
+      </c>
+      <c r="Q4">
+        <v>2.08</v>
+      </c>
+      <c r="R4">
+        <v>1.22</v>
+      </c>
+      <c r="S4">
+        <v>3.3</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.16</v>
+      </c>
+      <c r="W4">
+        <v>2.12</v>
+      </c>
+      <c r="X4">
+        <v>18</v>
+      </c>
+      <c r="Y4">
+        <v>25</v>
+      </c>
+      <c r="Z4">
+        <v>65</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>10.5</v>
+      </c>
+      <c r="AC4">
+        <v>12.5</v>
+      </c>
+      <c r="AD4">
+        <v>32</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>15</v>
+      </c>
+      <c r="AG4">
+        <v>15</v>
+      </c>
+      <c r="AH4">
+        <v>34</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>29</v>
+      </c>
+      <c r="AK4">
+        <v>30</v>
+      </c>
+      <c r="AL4">
+        <v>65</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>20</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>2.26</v>
+      </c>
+      <c r="AQ4">
+        <v>2.34</v>
+      </c>
+      <c r="AR4">
+        <v>2.48</v>
+      </c>
+      <c r="AS4">
+        <v>2.58</v>
+      </c>
+      <c r="AT4">
+        <v>2.06</v>
+      </c>
+      <c r="AU4">
+        <v>2.14</v>
+      </c>
+      <c r="AV4">
+        <v>2.38</v>
+      </c>
+      <c r="AW4">
+        <v>2.58</v>
+      </c>
+      <c r="AX4">
+        <v>2.2</v>
+      </c>
+      <c r="AY4">
+        <v>2.2</v>
+      </c>
+      <c r="AZ4">
+        <v>2.4</v>
+      </c>
+      <c r="BA4">
+        <v>2.58</v>
+      </c>
+      <c r="BB4">
+        <v>2.36</v>
+      </c>
+      <c r="BC4">
+        <v>2.38</v>
+      </c>
+      <c r="BD4">
+        <v>2.48</v>
+      </c>
+      <c r="BE4">
+        <v>2.58</v>
+      </c>
+      <c r="BF4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG4">
+        <v>2.58</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5">
+        <v>2.18</v>
+      </c>
+      <c r="G5">
+        <v>2.26</v>
+      </c>
+      <c r="H5">
+        <v>3.4</v>
+      </c>
+      <c r="I5">
+        <v>3.65</v>
+      </c>
+      <c r="J5">
+        <v>3.75</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>1.31</v>
+      </c>
+      <c r="M5">
+        <v>1.05</v>
+      </c>
+      <c r="N5">
+        <v>4.4</v>
+      </c>
+      <c r="O5">
+        <v>1.26</v>
+      </c>
+      <c r="P5">
+        <v>2.16</v>
+      </c>
+      <c r="Q5">
+        <v>1.76</v>
+      </c>
+      <c r="R5">
+        <v>1.46</v>
+      </c>
+      <c r="S5">
+        <v>2.92</v>
+      </c>
+      <c r="T5">
+        <v>1.66</v>
+      </c>
+      <c r="U5">
+        <v>2.3</v>
+      </c>
+      <c r="V5">
+        <v>1.37</v>
+      </c>
+      <c r="W5">
+        <v>1.79</v>
+      </c>
+      <c r="X5">
+        <v>22</v>
+      </c>
+      <c r="Y5">
+        <v>16</v>
+      </c>
+      <c r="Z5">
+        <v>32</v>
+      </c>
+      <c r="AA5">
+        <v>75</v>
+      </c>
+      <c r="AB5">
+        <v>12</v>
+      </c>
+      <c r="AC5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD5">
+        <v>15.5</v>
+      </c>
+      <c r="AE5">
+        <v>46</v>
+      </c>
+      <c r="AF5">
+        <v>15.5</v>
+      </c>
+      <c r="AG5">
+        <v>11.5</v>
+      </c>
+      <c r="AH5">
+        <v>17</v>
+      </c>
+      <c r="AI5">
+        <v>55</v>
+      </c>
+      <c r="AJ5">
+        <v>34</v>
+      </c>
+      <c r="AK5">
+        <v>23</v>
+      </c>
+      <c r="AL5">
+        <v>36</v>
+      </c>
+      <c r="AM5">
+        <v>90</v>
+      </c>
+      <c r="AN5">
+        <v>14</v>
+      </c>
+      <c r="AO5">
+        <v>34</v>
+      </c>
+      <c r="AP5">
+        <v>15.5</v>
+      </c>
+      <c r="AQ5">
+        <v>13.5</v>
+      </c>
+      <c r="AR5">
+        <v>21</v>
+      </c>
+      <c r="AS5">
+        <v>7.8</v>
+      </c>
+      <c r="AT5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU5">
+        <v>7.8</v>
+      </c>
+      <c r="AV5">
+        <v>13</v>
+      </c>
+      <c r="AW5">
+        <v>7.2</v>
+      </c>
+      <c r="AX5">
+        <v>13</v>
+      </c>
+      <c r="AY5">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5">
+        <v>14</v>
+      </c>
+      <c r="BA5">
+        <v>7.4</v>
+      </c>
+      <c r="BB5">
+        <v>7.2</v>
+      </c>
+      <c r="BC5">
+        <v>17.5</v>
+      </c>
+      <c r="BD5">
+        <v>6.8</v>
+      </c>
+      <c r="BE5">
+        <v>8</v>
+      </c>
+      <c r="BF5">
+        <v>11.5</v>
+      </c>
+      <c r="BG5">
+        <v>6.8</v>
+      </c>
+      <c r="BH5">
+        <v>5</v>
+      </c>
+      <c r="BI5">
+        <v>2.76</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>5.4</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>3.45</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>7.8</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>4.6</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6">
+        <v>2.56</v>
+      </c>
+      <c r="G6">
+        <v>3.4</v>
+      </c>
+      <c r="H6">
+        <v>2.2</v>
+      </c>
+      <c r="I6">
+        <v>3.05</v>
+      </c>
+      <c r="J6">
+        <v>3.4</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>2.32</v>
+      </c>
+      <c r="Q6">
+        <v>1.41</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7">
+        <v>2.7</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>1.24</v>
+      </c>
+      <c r="I7">
+        <v>3.4</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.24</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8">
+        <v>1.01</v>
+      </c>
+      <c r="G8">
+        <v>970</v>
+      </c>
+      <c r="H8">
+        <v>1.1</v>
+      </c>
+      <c r="I8">
+        <v>400</v>
+      </c>
+      <c r="J8">
+        <v>1.1</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.07</v>
+      </c>
+      <c r="Q8">
+        <v>1.02</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9">
+        <v>1.3</v>
+      </c>
+      <c r="G9">
+        <v>4.8</v>
+      </c>
+      <c r="H9">
+        <v>2.2</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.24</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10">
+        <v>1.27</v>
+      </c>
+      <c r="G10">
+        <v>1.34</v>
+      </c>
+      <c r="H10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I10">
+        <v>14</v>
+      </c>
+      <c r="J10">
+        <v>6.4</v>
+      </c>
+      <c r="K10">
+        <v>7.6</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>3.2</v>
+      </c>
+      <c r="Q10">
+        <v>1.38</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11">
+        <v>3.85</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>1.77</v>
+      </c>
+      <c r="I11">
+        <v>1.93</v>
+      </c>
+      <c r="J11">
+        <v>4.2</v>
+      </c>
+      <c r="K11">
+        <v>5.7</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2.58</v>
+      </c>
+      <c r="Q11">
+        <v>1.48</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>1.47</v>
+      </c>
+      <c r="U11">
+        <v>2.5</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11">
+        <v>1.01</v>
+      </c>
+      <c r="AR11">
+        <v>1.01</v>
+      </c>
+      <c r="AS11">
+        <v>1.01</v>
+      </c>
+      <c r="AT11">
+        <v>1.01</v>
+      </c>
+      <c r="AU11">
+        <v>7.4</v>
+      </c>
+      <c r="AV11">
+        <v>7.2</v>
+      </c>
+      <c r="AW11">
+        <v>1.01</v>
+      </c>
+      <c r="AX11">
+        <v>1.01</v>
+      </c>
+      <c r="AY11">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11">
+        <v>1.01</v>
+      </c>
+      <c r="BA11">
+        <v>1.01</v>
+      </c>
+      <c r="BB11">
+        <v>1.01</v>
+      </c>
+      <c r="BC11">
+        <v>1.01</v>
+      </c>
+      <c r="BD11">
+        <v>1.01</v>
+      </c>
+      <c r="BE11">
+        <v>1.01</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12">
+        <v>1.52</v>
+      </c>
+      <c r="G12">
+        <v>1.8</v>
+      </c>
+      <c r="H12">
+        <v>4.1</v>
+      </c>
+      <c r="I12">
+        <v>12.5</v>
+      </c>
+      <c r="J12">
+        <v>3.85</v>
+      </c>
+      <c r="K12">
+        <v>10.5</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.46</v>
+      </c>
+      <c r="Q12">
+        <v>1.36</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13">
+        <v>2.4</v>
+      </c>
+      <c r="G13">
+        <v>3.2</v>
+      </c>
+      <c r="H13">
+        <v>2.52</v>
+      </c>
+      <c r="I13">
+        <v>3.7</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>5.4</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.83</v>
+      </c>
+      <c r="Q13">
+        <v>1.69</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14">
+        <v>1.37</v>
+      </c>
+      <c r="G14">
+        <v>970</v>
+      </c>
+      <c r="H14">
+        <v>3.85</v>
+      </c>
+      <c r="I14">
+        <v>1000</v>
+      </c>
+      <c r="J14">
+        <v>1.01</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.07</v>
+      </c>
+      <c r="Q14">
+        <v>1.02</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1.01</v>
+      </c>
+      <c r="U14">
+        <v>1.01</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14">
+        <v>1.03</v>
+      </c>
+      <c r="AR14">
+        <v>1.03</v>
+      </c>
+      <c r="AS14">
+        <v>1.03</v>
+      </c>
+      <c r="AT14">
+        <v>1.03</v>
+      </c>
+      <c r="AU14">
+        <v>1.03</v>
+      </c>
+      <c r="AV14">
+        <v>1.03</v>
+      </c>
+      <c r="AW14">
+        <v>1.03</v>
+      </c>
+      <c r="AX14">
+        <v>1.03</v>
+      </c>
+      <c r="AY14">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14">
+        <v>1.03</v>
+      </c>
+      <c r="BA14">
+        <v>1.03</v>
+      </c>
+      <c r="BB14">
+        <v>1.03</v>
+      </c>
+      <c r="BC14">
+        <v>1.03</v>
+      </c>
+      <c r="BD14">
+        <v>1.03</v>
+      </c>
+      <c r="BE14">
+        <v>1.03</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15">
+        <v>1.15</v>
+      </c>
+      <c r="G15">
+        <v>1.16</v>
+      </c>
+      <c r="H15">
+        <v>21</v>
+      </c>
+      <c r="I15">
+        <v>34</v>
+      </c>
+      <c r="J15">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>11</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>3.95</v>
+      </c>
+      <c r="Q15">
+        <v>1.32</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16">
+        <v>1.31</v>
+      </c>
+      <c r="G16">
+        <v>1.37</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
+      <c r="J16">
+        <v>5.5</v>
+      </c>
+      <c r="K16">
+        <v>7.6</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>2.26</v>
+      </c>
+      <c r="Q16">
+        <v>1.48</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17">
+        <v>1.63</v>
+      </c>
+      <c r="G17">
+        <v>1.67</v>
+      </c>
+      <c r="H17">
+        <v>5.8</v>
+      </c>
+      <c r="I17">
+        <v>6.2</v>
+      </c>
+      <c r="J17">
+        <v>4.3</v>
+      </c>
+      <c r="K17">
+        <v>4.6</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1.05</v>
+      </c>
+      <c r="N17">
+        <v>4.8</v>
+      </c>
+      <c r="O17">
+        <v>1.24</v>
+      </c>
+      <c r="P17">
+        <v>2.3</v>
+      </c>
+      <c r="Q17">
+        <v>1.72</v>
+      </c>
+      <c r="R17">
+        <v>1.52</v>
+      </c>
+      <c r="S17">
+        <v>2.82</v>
+      </c>
+      <c r="T17">
+        <v>1.79</v>
+      </c>
+      <c r="U17">
+        <v>2.2</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>30</v>
+      </c>
+      <c r="Y17">
+        <v>36</v>
+      </c>
+      <c r="Z17">
+        <v>160</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>10</v>
+      </c>
+      <c r="AC17">
+        <v>10</v>
+      </c>
+      <c r="AD17">
+        <v>34</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>10.5</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+      <c r="AH17">
+        <v>27</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>16.5</v>
+      </c>
+      <c r="AK17">
+        <v>16</v>
+      </c>
+      <c r="AL17">
+        <v>50</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>7.8</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>17.5</v>
+      </c>
+      <c r="AQ17">
+        <v>17</v>
+      </c>
+      <c r="AR17">
+        <v>26</v>
+      </c>
+      <c r="AS17">
+        <v>42</v>
+      </c>
+      <c r="AT17">
+        <v>9</v>
+      </c>
+      <c r="AU17">
+        <v>9</v>
+      </c>
+      <c r="AV17">
+        <v>16.5</v>
+      </c>
+      <c r="AW17">
+        <v>32</v>
+      </c>
+      <c r="AX17">
+        <v>9.6</v>
+      </c>
+      <c r="AY17">
+        <v>9</v>
+      </c>
+      <c r="AZ17">
+        <v>17</v>
+      </c>
+      <c r="BA17">
+        <v>32</v>
+      </c>
+      <c r="BB17">
+        <v>14</v>
+      </c>
+      <c r="BC17">
+        <v>14</v>
+      </c>
+      <c r="BD17">
+        <v>19.5</v>
+      </c>
+      <c r="BE17">
+        <v>36</v>
+      </c>
+      <c r="BF17">
+        <v>7</v>
+      </c>
+      <c r="BG17">
+        <v>32</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="154">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,9 @@
     <t>Mexican Liga MX</t>
   </si>
   <si>
+    <t>Japanese J League</t>
+  </si>
+  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -286,12 +289,18 @@
     <t>Serbian Super League</t>
   </si>
   <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
     <t>Dutch Eredivisie</t>
   </si>
   <si>
     <t>English Sky Bet Championship</t>
   </si>
   <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
     <t>2026-09-11</t>
   </si>
   <si>
@@ -304,6 +313,9 @@
     <t>03:05:00</t>
   </si>
   <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
     <t>13:40:00</t>
   </si>
   <si>
@@ -325,12 +337,18 @@
     <t>16:30:00</t>
   </si>
   <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
     <t>18:00:00</t>
   </si>
   <si>
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
@@ -343,6 +361,12 @@
     <t>Pumas UNAM</t>
   </si>
   <si>
+    <t>Kobe</t>
+  </si>
+  <si>
+    <t>Kyoto</t>
+  </si>
+  <si>
     <t>Al-Khaleej Khor Fakkan</t>
   </si>
   <si>
@@ -370,6 +394,12 @@
     <t>Zeleznicar Pancevo</t>
   </si>
   <si>
+    <t>Lunds BK</t>
+  </si>
+  <si>
+    <t>FC Trollhattan</t>
+  </si>
+  <si>
     <t>AZ Alkmaar</t>
   </si>
   <si>
@@ -379,6 +409,9 @@
     <t>West Ham</t>
   </si>
   <si>
+    <t>Belouizdad</t>
+  </si>
+  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
@@ -391,6 +424,12 @@
     <t>Leon</t>
   </si>
   <si>
+    <t>Kashima</t>
+  </si>
+  <si>
+    <t>Kashiwa</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
@@ -418,6 +457,12 @@
     <t>Macva Sabac</t>
   </si>
   <si>
+    <t>Rosengard</t>
+  </si>
+  <si>
+    <t>Utsiktens</t>
+  </si>
+  <si>
     <t>Willem II</t>
   </si>
   <si>
@@ -427,7 +472,10 @@
     <t>Wrexham</t>
   </si>
   <si>
-    <t>2026-09-09 02:17:26</t>
+    <t>ES Setif</t>
+  </si>
+  <si>
+    <t>2026-09-09 09:00:48</t>
   </si>
 </sst>
 </file>
@@ -759,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1009,241 +1057,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H2">
         <v>14</v>
       </c>
       <c r="I2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="K2">
         <v>10</v>
       </c>
       <c r="L2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="O2">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="Q2">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="R2">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="S2">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="T2">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W2">
         <v>5.4</v>
       </c>
       <c r="X2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Y2">
         <v>60</v>
       </c>
       <c r="Z2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AC2">
+        <v>27</v>
+      </c>
+      <c r="AD2">
+        <v>70</v>
+      </c>
+      <c r="AE2">
+        <v>370</v>
+      </c>
+      <c r="AF2">
+        <v>10.5</v>
+      </c>
+      <c r="AG2">
+        <v>16</v>
+      </c>
+      <c r="AH2">
+        <v>44</v>
+      </c>
+      <c r="AI2">
+        <v>240</v>
+      </c>
+      <c r="AJ2">
+        <v>10</v>
+      </c>
+      <c r="AK2">
+        <v>14</v>
+      </c>
+      <c r="AL2">
+        <v>60</v>
+      </c>
+      <c r="AM2">
+        <v>270</v>
+      </c>
+      <c r="AN2">
+        <v>3.15</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>6.2</v>
+      </c>
+      <c r="AQ2">
+        <v>6.4</v>
+      </c>
+      <c r="AR2">
+        <v>7</v>
+      </c>
+      <c r="AS2">
+        <v>6.6</v>
+      </c>
+      <c r="AT2">
+        <v>11</v>
+      </c>
+      <c r="AU2">
+        <v>18.5</v>
+      </c>
+      <c r="AV2">
+        <v>6.4</v>
+      </c>
+      <c r="AW2">
+        <v>6.4</v>
+      </c>
+      <c r="AX2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY2">
+        <v>13</v>
+      </c>
+      <c r="AZ2">
+        <v>6.2</v>
+      </c>
+      <c r="BA2">
+        <v>7</v>
+      </c>
+      <c r="BB2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC2">
+        <v>11</v>
+      </c>
+      <c r="BD2">
+        <v>6.4</v>
+      </c>
+      <c r="BE2">
+        <v>6.4</v>
+      </c>
+      <c r="BF2">
+        <v>2.66</v>
+      </c>
+      <c r="BG2">
+        <v>6.6</v>
+      </c>
+      <c r="BH2">
+        <v>5.2</v>
+      </c>
+      <c r="BI2">
+        <v>4</v>
+      </c>
+      <c r="BJ2">
+        <v>15.5</v>
+      </c>
+      <c r="BK2">
+        <v>6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>9.6</v>
+      </c>
+      <c r="BN2">
+        <v>3.85</v>
+      </c>
+      <c r="BO2">
+        <v>3.25</v>
+      </c>
+      <c r="BP2">
+        <v>6.4</v>
+      </c>
+      <c r="BQ2">
+        <v>4.8</v>
+      </c>
+      <c r="BR2">
+        <v>24</v>
+      </c>
+      <c r="BS2">
+        <v>7</v>
+      </c>
+      <c r="BT2">
         <v>21</v>
       </c>
-      <c r="AD2">
-        <v>75</v>
-      </c>
-      <c r="AE2">
-        <v>430</v>
-      </c>
-      <c r="AF2">
-        <v>8.4</v>
-      </c>
-      <c r="AG2">
-        <v>16.5</v>
-      </c>
-      <c r="AH2">
-        <v>60</v>
-      </c>
-      <c r="AI2">
-        <v>290</v>
-      </c>
-      <c r="AJ2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK2">
-        <v>18.5</v>
-      </c>
-      <c r="AL2">
-        <v>65</v>
-      </c>
-      <c r="AM2">
-        <v>340</v>
-      </c>
-      <c r="AN2">
-        <v>3.7</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>5.3</v>
-      </c>
-      <c r="AQ2">
-        <v>5.7</v>
-      </c>
-      <c r="AR2">
-        <v>6.2</v>
-      </c>
-      <c r="AS2">
-        <v>6.4</v>
-      </c>
-      <c r="AT2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU2">
-        <v>17.5</v>
-      </c>
-      <c r="AV2">
-        <v>5.8</v>
-      </c>
-      <c r="AW2">
-        <v>6.2</v>
-      </c>
-      <c r="AX2">
-        <v>7</v>
-      </c>
-      <c r="AY2">
-        <v>12</v>
-      </c>
-      <c r="AZ2">
-        <v>5.7</v>
-      </c>
-      <c r="BA2">
-        <v>6.2</v>
-      </c>
-      <c r="BB2">
-        <v>7.2</v>
-      </c>
-      <c r="BC2">
-        <v>13</v>
-      </c>
-      <c r="BD2">
-        <v>5.8</v>
-      </c>
-      <c r="BE2">
-        <v>6.2</v>
-      </c>
-      <c r="BF2">
-        <v>3.15</v>
-      </c>
-      <c r="BG2">
-        <v>6.2</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.28</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.28</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.28</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.01</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.28</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.28</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
       <c r="BU2">
-        <v>1.28</v>
+        <v>6.8</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.28</v>
+        <v>9.6</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.28</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA2">
-        <v>1.28</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1251,37 +1299,37 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F3">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G3">
         <v>2.86</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I3">
         <v>3.15</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1299,16 +1347,16 @@
         <v>2.34</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T3">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U3">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V3">
         <v>1.46</v>
@@ -1320,28 +1368,28 @@
         <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB3">
         <v>11</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
+        <v>14.5</v>
+      </c>
+      <c r="AE3">
+        <v>48</v>
+      </c>
+      <c r="AF3">
         <v>17</v>
-      </c>
-      <c r="AE3">
-        <v>50</v>
-      </c>
-      <c r="AF3">
-        <v>17.5</v>
       </c>
       <c r="AG3">
         <v>13</v>
@@ -1350,10 +1398,10 @@
         <v>20</v>
       </c>
       <c r="AI3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK3">
         <v>36</v>
@@ -1362,13 +1410,13 @@
         <v>65</v>
       </c>
       <c r="AM3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN3">
         <v>42</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP3">
         <v>9</v>
@@ -1380,46 +1428,46 @@
         <v>17</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
         <v>12</v>
       </c>
       <c r="AW3">
+        <v>34</v>
+      </c>
+      <c r="AX3">
+        <v>15</v>
+      </c>
+      <c r="AY3">
+        <v>11.5</v>
+      </c>
+      <c r="AZ3">
+        <v>17.5</v>
+      </c>
+      <c r="BA3">
+        <v>50</v>
+      </c>
+      <c r="BB3">
         <v>32</v>
       </c>
-      <c r="AX3">
-        <v>14</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
-      <c r="AZ3">
-        <v>17</v>
-      </c>
-      <c r="BA3">
-        <v>6</v>
-      </c>
-      <c r="BB3">
+      <c r="BC3">
         <v>30</v>
       </c>
-      <c r="BC3">
-        <v>5.6</v>
-      </c>
       <c r="BD3">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="BE3">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
-        <v>5.8</v>
+        <v>27</v>
       </c>
       <c r="BG3">
         <v>36</v>
@@ -1434,31 +1482,31 @@
         <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN3">
         <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BR3">
         <v>50</v>
       </c>
       <c r="BS3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BT3">
         <v>7</v>
@@ -1470,22 +1518,22 @@
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX3">
         <v>55</v>
       </c>
       <c r="BY3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ3">
         <v>50</v>
       </c>
       <c r="CA3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="CB3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1493,178 +1541,178 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F4">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="G4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H4">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
         <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X4">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="Z4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC4">
         <v>10.5</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
+        <v>27</v>
+      </c>
+      <c r="AE4">
+        <v>110</v>
+      </c>
+      <c r="AF4">
         <v>12.5</v>
       </c>
-      <c r="AD4">
-        <v>32</v>
-      </c>
-      <c r="AE4">
-        <v>1000</v>
-      </c>
-      <c r="AF4">
-        <v>15</v>
-      </c>
       <c r="AG4">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AK4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP4">
-        <v>2.26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>2.34</v>
+        <v>12</v>
       </c>
       <c r="AR4">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="AS4">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="AT4">
-        <v>2.06</v>
+        <v>5.6</v>
       </c>
       <c r="AU4">
-        <v>2.14</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>2.38</v>
+        <v>18.5</v>
       </c>
       <c r="AW4">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="AX4">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY4">
-        <v>2.2</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>2.4</v>
+        <v>19</v>
       </c>
       <c r="BA4">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="BB4">
-        <v>2.36</v>
+        <v>16</v>
       </c>
       <c r="BC4">
-        <v>2.38</v>
+        <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="BE4">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="BF4">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG4">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1727,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1735,16 +1783,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F5">
         <v>2.18</v>
@@ -1753,10 +1801,10 @@
         <v>2.26</v>
       </c>
       <c r="H5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
         <v>3.75</v>
@@ -1783,7 +1831,7 @@
         <v>1.76</v>
       </c>
       <c r="R5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S5">
         <v>2.92</v>
@@ -1795,13 +1843,13 @@
         <v>2.3</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
         <v>1.79</v>
       </c>
       <c r="X5">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y5">
         <v>16</v>
@@ -1837,7 +1885,7 @@
         <v>55</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK5">
         <v>23</v>
@@ -1864,7 +1912,7 @@
         <v>21</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
         <v>9.800000000000001</v>
@@ -1876,7 +1924,7 @@
         <v>13</v>
       </c>
       <c r="AW5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX5">
         <v>13</v>
@@ -1888,25 +1936,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC5">
         <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH5">
         <v>5</v>
@@ -1969,7 +2017,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1977,524 +2025,524 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F6">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="G6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H6">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I6">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>1.76</v>
       </c>
       <c r="Q6">
-        <v>1.41</v>
+        <v>2.18</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="CB6" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7">
+        <v>4.2</v>
+      </c>
+      <c r="G7">
+        <v>4.6</v>
+      </c>
+      <c r="H7">
+        <v>1.89</v>
+      </c>
+      <c r="I7">
+        <v>1.98</v>
+      </c>
+      <c r="J7">
+        <v>3.8</v>
+      </c>
+      <c r="K7">
+        <v>4.1</v>
+      </c>
+      <c r="L7">
+        <v>1.33</v>
+      </c>
+      <c r="M7">
+        <v>1.06</v>
+      </c>
+      <c r="N7">
+        <v>4.2</v>
+      </c>
+      <c r="O7">
+        <v>1.27</v>
+      </c>
+      <c r="P7">
+        <v>2.1</v>
+      </c>
+      <c r="Q7">
+        <v>1.79</v>
+      </c>
+      <c r="R7">
+        <v>1.44</v>
+      </c>
+      <c r="S7">
+        <v>3.05</v>
+      </c>
+      <c r="T7">
+        <v>1.74</v>
+      </c>
+      <c r="U7">
+        <v>2.2</v>
+      </c>
+      <c r="V7">
+        <v>2.02</v>
+      </c>
+      <c r="W7">
+        <v>1.27</v>
+      </c>
+      <c r="X7">
+        <v>20</v>
+      </c>
+      <c r="Y7">
+        <v>10.5</v>
+      </c>
+      <c r="Z7">
+        <v>13</v>
+      </c>
+      <c r="AA7">
+        <v>23</v>
+      </c>
+      <c r="AB7">
+        <v>18</v>
+      </c>
+      <c r="AC7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD7">
+        <v>11</v>
+      </c>
+      <c r="AE7">
+        <v>20</v>
+      </c>
+      <c r="AF7">
+        <v>40</v>
+      </c>
+      <c r="AG7">
+        <v>18.5</v>
+      </c>
+      <c r="AH7">
+        <v>18.5</v>
+      </c>
+      <c r="AI7">
+        <v>38</v>
+      </c>
+      <c r="AJ7">
         <v>110</v>
       </c>
-      <c r="E7" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7">
-        <v>2.7</v>
-      </c>
-      <c r="G7">
-        <v>1000</v>
-      </c>
-      <c r="H7">
-        <v>1.24</v>
-      </c>
-      <c r="I7">
-        <v>3.4</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>950</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>1.24</v>
-      </c>
-      <c r="Q7">
-        <v>1.01</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
       <c r="AK7">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="CB7" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F8">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="G8">
-        <v>970</v>
+        <v>3.1</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>2.26</v>
       </c>
       <c r="I8">
-        <v>400</v>
+        <v>2.58</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2503,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.07</v>
+        <v>2.32</v>
       </c>
       <c r="Q8">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2515,10 +2563,10 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2527,112 +2575,112 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH8">
         <v>0</v>
@@ -2695,36 +2743,36 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F9">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="G9">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J9">
         <v>3</v>
@@ -2937,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2945,40 +2993,40 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F10">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="G10">
-        <v>1.34</v>
+        <v>970</v>
       </c>
       <c r="H10">
-        <v>9.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="I10">
-        <v>14</v>
+        <v>400</v>
       </c>
       <c r="J10">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2987,10 +3035,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>3.2</v>
+        <v>1.07</v>
       </c>
       <c r="Q10">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2999,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -3011,112 +3059,112 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>0</v>
@@ -3179,61 +3227,61 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F11">
-        <v>3.85</v>
+        <v>1.3</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H11">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="I11">
-        <v>1.93</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.24</v>
+      </c>
+      <c r="Q11">
         <v>1.01</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>2.58</v>
-      </c>
-      <c r="Q11">
-        <v>1.48</v>
-      </c>
       <c r="R11">
         <v>0</v>
       </c>
@@ -3241,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3253,112 +3301,112 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU11">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH11">
         <v>0</v>
@@ -3421,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3429,34 +3477,34 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F12">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="G12">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="H12">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I12">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="J12">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="K12">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3471,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="Q12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3663,48 +3711,48 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F13">
-        <v>2.4</v>
+        <v>3.95</v>
       </c>
       <c r="G13">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="H13">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="I13">
-        <v>3.7</v>
+        <v>1.91</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="K13">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3713,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="Q13">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3725,10 +3773,10 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3737,112 +3785,112 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH13">
         <v>0</v>
@@ -3905,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3913,40 +3961,40 @@
         <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F14">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="G14">
-        <v>970</v>
+        <v>2.04</v>
       </c>
       <c r="H14">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J14">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3955,10 +4003,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.07</v>
+        <v>2.46</v>
       </c>
       <c r="Q14">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -3967,10 +4015,10 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3979,112 +4027,112 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH14">
         <v>0</v>
@@ -4147,42 +4195,42 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F15">
-        <v>1.15</v>
+        <v>2.42</v>
       </c>
       <c r="G15">
-        <v>1.16</v>
+        <v>2.78</v>
       </c>
       <c r="H15">
-        <v>21</v>
+        <v>2.72</v>
       </c>
       <c r="I15">
-        <v>34</v>
+        <v>3.15</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4197,10 +4245,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>3.95</v>
+        <v>1.99</v>
       </c>
       <c r="Q15">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4389,48 +4437,48 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="F16">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="G16">
-        <v>1.37</v>
+        <v>2.24</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="I16">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="J16">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="K16">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4439,10 +4487,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.26</v>
+        <v>1.07</v>
       </c>
       <c r="Q16">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4451,10 +4499,10 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4463,112 +4511,112 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>0</v>
@@ -4631,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4639,241 +4687,1451 @@
         <v>91</v>
       </c>
       <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17">
+        <v>1.01</v>
+      </c>
+      <c r="G17">
+        <v>1000</v>
+      </c>
+      <c r="H17">
+        <v>1.01</v>
+      </c>
+      <c r="I17">
+        <v>1000</v>
+      </c>
+      <c r="J17">
+        <v>1.01</v>
+      </c>
+      <c r="K17">
+        <v>1000</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1.07</v>
+      </c>
+      <c r="Q17">
+        <v>1.01</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18">
+        <v>1.01</v>
+      </c>
+      <c r="G18">
+        <v>1000</v>
+      </c>
+      <c r="H18">
+        <v>1.01</v>
+      </c>
+      <c r="I18">
+        <v>1000</v>
+      </c>
+      <c r="J18">
+        <v>1.01</v>
+      </c>
+      <c r="K18">
+        <v>1000</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.07</v>
+      </c>
+      <c r="Q18">
+        <v>1.01</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
         <v>92</v>
       </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F17">
-        <v>1.63</v>
-      </c>
-      <c r="G17">
-        <v>1.67</v>
-      </c>
-      <c r="H17">
-        <v>5.8</v>
-      </c>
-      <c r="I17">
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F19">
+        <v>1.17</v>
+      </c>
+      <c r="G19">
+        <v>1.18</v>
+      </c>
+      <c r="H19">
+        <v>21</v>
+      </c>
+      <c r="I19">
+        <v>27</v>
+      </c>
+      <c r="J19">
+        <v>9.4</v>
+      </c>
+      <c r="K19">
+        <v>10.5</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>3.8</v>
+      </c>
+      <c r="Q19">
+        <v>1.32</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20">
+        <v>1.3</v>
+      </c>
+      <c r="G20">
+        <v>1.36</v>
+      </c>
+      <c r="H20">
+        <v>10.5</v>
+      </c>
+      <c r="I20">
+        <v>15</v>
+      </c>
+      <c r="J20">
+        <v>5.6</v>
+      </c>
+      <c r="K20">
+        <v>6.8</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>2.38</v>
+      </c>
+      <c r="Q20">
+        <v>1.56</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21">
+        <v>1.64</v>
+      </c>
+      <c r="G21">
+        <v>1.66</v>
+      </c>
+      <c r="H21">
+        <v>5.7</v>
+      </c>
+      <c r="I21">
         <v>6.2</v>
       </c>
-      <c r="J17">
+      <c r="J21">
         <v>4.3</v>
       </c>
-      <c r="K17">
+      <c r="K21">
         <v>4.6</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>1.05</v>
       </c>
-      <c r="N17">
-        <v>4.8</v>
-      </c>
-      <c r="O17">
-        <v>1.24</v>
-      </c>
-      <c r="P17">
-        <v>2.3</v>
-      </c>
-      <c r="Q17">
-        <v>1.72</v>
-      </c>
-      <c r="R17">
+      <c r="N21">
+        <v>4.9</v>
+      </c>
+      <c r="O21">
+        <v>1.23</v>
+      </c>
+      <c r="P21">
+        <v>2.32</v>
+      </c>
+      <c r="Q21">
+        <v>1.69</v>
+      </c>
+      <c r="R21">
         <v>1.52</v>
       </c>
-      <c r="S17">
-        <v>2.82</v>
-      </c>
-      <c r="T17">
-        <v>1.79</v>
-      </c>
-      <c r="U17">
-        <v>2.2</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>30</v>
-      </c>
-      <c r="Y17">
+      <c r="S21">
+        <v>2.76</v>
+      </c>
+      <c r="T21">
+        <v>1.77</v>
+      </c>
+      <c r="U21">
+        <v>2.22</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>21</v>
+      </c>
+      <c r="Y21">
+        <v>25</v>
+      </c>
+      <c r="Z21">
+        <v>60</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>10.5</v>
+      </c>
+      <c r="AC21">
+        <v>10.5</v>
+      </c>
+      <c r="AD21">
+        <v>24</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>11</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+      <c r="AH21">
+        <v>21</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>16.5</v>
+      </c>
+      <c r="AK21">
+        <v>16.5</v>
+      </c>
+      <c r="AL21">
+        <v>50</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>7.6</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>17.5</v>
+      </c>
+      <c r="AQ21">
+        <v>20</v>
+      </c>
+      <c r="AR21">
+        <v>26</v>
+      </c>
+      <c r="AS21">
+        <v>42</v>
+      </c>
+      <c r="AT21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU21">
+        <v>9</v>
+      </c>
+      <c r="AV21">
+        <v>16</v>
+      </c>
+      <c r="AW21">
+        <v>32</v>
+      </c>
+      <c r="AX21">
+        <v>9.6</v>
+      </c>
+      <c r="AY21">
+        <v>9</v>
+      </c>
+      <c r="AZ21">
+        <v>16.5</v>
+      </c>
+      <c r="BA21">
+        <v>46</v>
+      </c>
+      <c r="BB21">
+        <v>14</v>
+      </c>
+      <c r="BC21">
+        <v>14</v>
+      </c>
+      <c r="BD21">
+        <v>19.5</v>
+      </c>
+      <c r="BE21">
         <v>36</v>
       </c>
-      <c r="Z17">
-        <v>160</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>10</v>
-      </c>
-      <c r="AC17">
-        <v>10</v>
-      </c>
-      <c r="AD17">
-        <v>34</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
+      <c r="BF21">
+        <v>7</v>
+      </c>
+      <c r="BG21">
+        <v>44</v>
+      </c>
+      <c r="BH21">
+        <v>3.95</v>
+      </c>
+      <c r="BI21">
+        <v>3.65</v>
+      </c>
+      <c r="BJ21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK21">
+        <v>6.2</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>14.5</v>
+      </c>
+      <c r="BN21">
+        <v>4.4</v>
+      </c>
+      <c r="BO21">
+        <v>3.95</v>
+      </c>
+      <c r="BP21">
         <v>10.5</v>
       </c>
-      <c r="AG17">
-        <v>10</v>
-      </c>
-      <c r="AH17">
-        <v>27</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>16.5</v>
-      </c>
-      <c r="AK17">
+      <c r="BQ21">
+        <v>6.4</v>
+      </c>
+      <c r="BR21">
+        <v>23</v>
+      </c>
+      <c r="BS21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT21">
+        <v>9.4</v>
+      </c>
+      <c r="BU21">
+        <v>6</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>12.5</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>12.5</v>
+      </c>
+      <c r="BZ21">
         <v>16</v>
       </c>
-      <c r="AL17">
-        <v>50</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>7.8</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>17.5</v>
-      </c>
-      <c r="AQ17">
-        <v>17</v>
-      </c>
-      <c r="AR17">
-        <v>26</v>
-      </c>
-      <c r="AS17">
-        <v>42</v>
-      </c>
-      <c r="AT17">
-        <v>9</v>
-      </c>
-      <c r="AU17">
-        <v>9</v>
-      </c>
-      <c r="AV17">
-        <v>16.5</v>
-      </c>
-      <c r="AW17">
-        <v>32</v>
-      </c>
-      <c r="AX17">
-        <v>9.6</v>
-      </c>
-      <c r="AY17">
-        <v>9</v>
-      </c>
-      <c r="AZ17">
-        <v>17</v>
-      </c>
-      <c r="BA17">
-        <v>32</v>
-      </c>
-      <c r="BB17">
-        <v>14</v>
-      </c>
-      <c r="BC17">
-        <v>14</v>
-      </c>
-      <c r="BD17">
-        <v>19.5</v>
-      </c>
-      <c r="BE17">
-        <v>36</v>
-      </c>
-      <c r="BF17">
-        <v>7</v>
-      </c>
-      <c r="BG17">
-        <v>32</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
+      <c r="CA21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22">
         <v>1.01</v>
       </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
+      <c r="G22">
+        <v>1000</v>
+      </c>
+      <c r="H22">
         <v>1.01</v>
       </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
+      <c r="I22">
+        <v>1000</v>
+      </c>
+      <c r="J22">
         <v>1.01</v>
       </c>
-      <c r="BN17">
-        <v>1000</v>
-      </c>
-      <c r="BO17">
+      <c r="K22">
+        <v>950</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1.07</v>
+      </c>
+      <c r="Q22">
         <v>1.01</v>
       </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>1.01</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>1.01</v>
-      </c>
-      <c r="BT17">
-        <v>1000</v>
-      </c>
-      <c r="BU17">
-        <v>1.01</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>1.01</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>1.01</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
-      <c r="CA17">
-        <v>1.01</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>137</v>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="165">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,15 @@
     <t>Japanese J League</t>
   </si>
   <si>
+    <t>Indonesian Super League</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premier League</t>
+  </si>
+  <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -316,6 +325,12 @@
     <t>10:00:00</t>
   </si>
   <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
     <t>13:40:00</t>
   </si>
   <si>
@@ -367,18 +382,27 @@
     <t>Kyoto</t>
   </si>
   <si>
+    <t>Dewa United FC</t>
+  </si>
+  <si>
+    <t>Imisli FK</t>
+  </si>
+  <si>
+    <t>Kolos Kovalyovka</t>
+  </si>
+  <si>
     <t>Al-Khaleej Khor Fakkan</t>
   </si>
   <si>
     <t>Ogre United</t>
   </si>
   <si>
+    <t>FK Riga</t>
+  </si>
+  <si>
     <t>Ararat Armenia</t>
   </si>
   <si>
-    <t>FK Riga</t>
-  </si>
-  <si>
     <t>Al-Quadisiya (KSA)</t>
   </si>
   <si>
@@ -430,18 +454,27 @@
     <t>Kashiwa</t>
   </si>
   <si>
+    <t>Bhayangkara FC</t>
+  </si>
+  <si>
+    <t>Neftchi Baku</t>
+  </si>
+  <si>
+    <t>Karpaty</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
     <t>Liepajas Metalurgs</t>
   </si>
   <si>
+    <t>FK Auda</t>
+  </si>
+  <si>
     <t>FC Syunik</t>
   </si>
   <si>
-    <t>FK Auda</t>
-  </si>
-  <si>
     <t>Al-Ettifaq</t>
   </si>
   <si>
@@ -475,7 +508,7 @@
     <t>ES Setif</t>
   </si>
   <si>
-    <t>2026-09-09 09:00:48</t>
+    <t>2026-09-09 11:33:30</t>
   </si>
 </sst>
 </file>
@@ -807,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1057,43 +1090,43 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F2">
         <v>1.2</v>
       </c>
       <c r="G2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O2">
         <v>1.15</v>
@@ -1102,28 +1135,28 @@
         <v>3</v>
       </c>
       <c r="Q2">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="R2">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="X2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y2">
         <v>60</v>
@@ -1135,10 +1168,10 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AD2">
         <v>70</v>
@@ -1147,13 +1180,13 @@
         <v>370</v>
       </c>
       <c r="AF2">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI2">
         <v>240</v>
@@ -1165,40 +1198,40 @@
         <v>14</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AN2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AR2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS2">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT2">
         <v>11</v>
       </c>
       <c r="AU2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AV2">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW2">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
         <v>8.199999999999999</v>
@@ -1207,49 +1240,49 @@
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC2">
         <v>11</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF2">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH2">
         <v>5.2</v>
       </c>
       <c r="BI2">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2">
         <v>15.5</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BO2">
         <v>3.25</v>
@@ -1258,31 +1291,31 @@
         <v>6.4</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BR2">
         <v>24</v>
       </c>
       <c r="BS2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT2">
         <v>21</v>
       </c>
       <c r="BU2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>8.199999999999999</v>
@@ -1291,7 +1324,7 @@
         <v>6</v>
       </c>
       <c r="CB2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1299,28 +1332,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F3">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H3">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J3">
         <v>3.15</v>
@@ -1329,7 +1362,7 @@
         <v>3.25</v>
       </c>
       <c r="L3">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1341,7 +1374,7 @@
         <v>1.45</v>
       </c>
       <c r="P3">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
         <v>2.34</v>
@@ -1353,16 +1386,16 @@
         <v>4.5</v>
       </c>
       <c r="T3">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U3">
         <v>1.94</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
         <v>12.5</v>
@@ -1371,22 +1404,22 @@
         <v>11</v>
       </c>
       <c r="Z3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA3">
         <v>55</v>
       </c>
       <c r="AB3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
         <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>17</v>
@@ -1404,34 +1437,34 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP3">
         <v>9</v>
       </c>
       <c r="AQ3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR3">
         <v>17</v>
       </c>
       <c r="AS3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
@@ -1440,7 +1473,7 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX3">
         <v>15</v>
@@ -1464,16 +1497,16 @@
         <v>46</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF3">
         <v>27</v>
       </c>
       <c r="BG3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BH3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI3">
         <v>2.38</v>
@@ -1500,7 +1533,7 @@
         <v>28</v>
       </c>
       <c r="BQ3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR3">
         <v>50</v>
@@ -1509,7 +1542,7 @@
         <v>4.7</v>
       </c>
       <c r="BT3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU3">
         <v>5.2</v>
@@ -1533,7 +1566,7 @@
         <v>4.7</v>
       </c>
       <c r="CB3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1541,22 +1574,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F4">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G4">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H4">
         <v>5.2</v>
@@ -1568,7 +1601,7 @@
         <v>3.55</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1580,13 +1613,13 @@
         <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
         <v>1.27</v>
@@ -1604,13 +1637,13 @@
         <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X4">
         <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z4">
         <v>55</v>
@@ -1631,7 +1664,7 @@
         <v>110</v>
       </c>
       <c r="AF4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG4">
         <v>12.5</v>
@@ -1643,7 +1676,7 @@
         <v>120</v>
       </c>
       <c r="AJ4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK4">
         <v>26</v>
@@ -1661,22 +1694,22 @@
         <v>160</v>
       </c>
       <c r="AP4">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
         <v>12</v>
       </c>
       <c r="AR4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AS4">
         <v>4.3</v>
       </c>
       <c r="AT4">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
         <v>18.5</v>
@@ -1685,7 +1718,7 @@
         <v>4.2</v>
       </c>
       <c r="AX4">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY4">
         <v>8.6</v>
@@ -1697,13 +1730,13 @@
         <v>4.2</v>
       </c>
       <c r="BB4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC4">
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE4">
         <v>4.3</v>
@@ -1712,70 +1745,70 @@
         <v>10.5</v>
       </c>
       <c r="BG4">
+        <v>4.2</v>
+      </c>
+      <c r="BH4">
+        <v>3.65</v>
+      </c>
+      <c r="BI4">
+        <v>2.54</v>
+      </c>
+      <c r="BJ4">
+        <v>13.5</v>
+      </c>
+      <c r="BK4">
+        <v>3.55</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>4.7</v>
+      </c>
+      <c r="BN4">
+        <v>5</v>
+      </c>
+      <c r="BO4">
+        <v>3.3</v>
+      </c>
+      <c r="BP4">
+        <v>15.5</v>
+      </c>
+      <c r="BQ4">
+        <v>3.7</v>
+      </c>
+      <c r="BR4">
+        <v>38</v>
+      </c>
+      <c r="BS4">
         <v>4.3</v>
       </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4">
-        <v>1000</v>
-      </c>
-      <c r="BK4">
-        <v>1.01</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.01</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.01</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.01</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.01</v>
-      </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB4" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1783,16 +1816,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F5">
         <v>2.18</v>
@@ -1801,16 +1834,16 @@
         <v>2.26</v>
       </c>
       <c r="H5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
         <v>1.31</v>
@@ -1819,25 +1852,25 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R5">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S5">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U5">
         <v>2.3</v>
@@ -1897,7 +1930,7 @@
         <v>90</v>
       </c>
       <c r="AN5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO5">
         <v>34</v>
@@ -1912,7 +1945,7 @@
         <v>21</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5">
         <v>9.800000000000001</v>
@@ -1924,10 +1957,10 @@
         <v>13</v>
       </c>
       <c r="AW5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY5">
         <v>9.4</v>
@@ -1936,25 +1969,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC5">
         <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF5">
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH5">
         <v>5</v>
@@ -2017,7 +2050,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2025,22 +2058,22 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F6">
         <v>3.1</v>
       </c>
       <c r="G6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H6">
         <v>2.5</v>
@@ -2049,7 +2082,7 @@
         <v>2.62</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
         <v>3.45</v>
@@ -2088,121 +2121,121 @@
         <v>1.61</v>
       </c>
       <c r="W6">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Y6">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="Z6">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC6">
+        <v>970</v>
+      </c>
+      <c r="AD6">
+        <v>970</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>970</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>7.8</v>
+      </c>
+      <c r="AQ6">
+        <v>6.8</v>
+      </c>
+      <c r="AR6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS6">
+        <v>1.46</v>
+      </c>
+      <c r="AT6">
         <v>7.6</v>
       </c>
-      <c r="AD6">
-        <v>12</v>
-      </c>
-      <c r="AE6">
-        <v>32</v>
-      </c>
-      <c r="AF6">
-        <v>22</v>
-      </c>
-      <c r="AG6">
-        <v>14</v>
-      </c>
-      <c r="AH6">
-        <v>18.5</v>
-      </c>
-      <c r="AI6">
-        <v>65</v>
-      </c>
-      <c r="AJ6">
-        <v>85</v>
-      </c>
-      <c r="AK6">
-        <v>42</v>
-      </c>
-      <c r="AL6">
-        <v>75</v>
-      </c>
-      <c r="AM6">
-        <v>130</v>
-      </c>
-      <c r="AN6">
-        <v>60</v>
-      </c>
-      <c r="AO6">
-        <v>30</v>
-      </c>
-      <c r="AP6">
-        <v>10.5</v>
-      </c>
-      <c r="AQ6">
-        <v>8.4</v>
-      </c>
-      <c r="AR6">
-        <v>14</v>
-      </c>
-      <c r="AS6">
-        <v>26</v>
-      </c>
-      <c r="AT6">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AU6">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AV6">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>10</v>
+        <v>1.46</v>
       </c>
       <c r="AX6">
-        <v>18.5</v>
+        <v>1.46</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA6">
-        <v>11</v>
+        <v>1.46</v>
       </c>
       <c r="BB6">
-        <v>11.5</v>
+        <v>1.46</v>
       </c>
       <c r="BC6">
-        <v>11</v>
+        <v>1.46</v>
       </c>
       <c r="BD6">
-        <v>11.5</v>
+        <v>1.46</v>
       </c>
       <c r="BE6">
-        <v>13</v>
+        <v>1.46</v>
       </c>
       <c r="BF6">
-        <v>11</v>
+        <v>1.46</v>
       </c>
       <c r="BG6">
-        <v>9.6</v>
+        <v>1.46</v>
       </c>
       <c r="BH6">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
@@ -2214,7 +2247,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="BN6">
         <v>1000</v>
@@ -2226,13 +2259,13 @@
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="BT6">
         <v>1000</v>
@@ -2244,22 +2277,22 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="CB6" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2267,16 +2300,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F7">
         <v>4.2</v>
@@ -2288,7 +2321,7 @@
         <v>1.89</v>
       </c>
       <c r="I7">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J7">
         <v>3.8</v>
@@ -2312,7 +2345,7 @@
         <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R7">
         <v>1.44</v>
@@ -2333,7 +2366,7 @@
         <v>1.27</v>
       </c>
       <c r="X7">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y7">
         <v>10.5</v>
@@ -2348,7 +2381,7 @@
         <v>18</v>
       </c>
       <c r="AC7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>11</v>
@@ -2411,7 +2444,7 @@
         <v>16</v>
       </c>
       <c r="AX7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY7">
         <v>15</v>
@@ -2420,22 +2453,22 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB7">
+        <v>8.4</v>
+      </c>
+      <c r="BC7">
         <v>8</v>
       </c>
-      <c r="BC7">
-        <v>7.6</v>
-      </c>
       <c r="BD7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE7">
+        <v>8.4</v>
+      </c>
+      <c r="BF7">
         <v>8</v>
-      </c>
-      <c r="BF7">
-        <v>7.6</v>
       </c>
       <c r="BG7">
         <v>9.800000000000001</v>
@@ -2444,7 +2477,7 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.96</v>
+        <v>1.47</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
@@ -2501,7 +2534,7 @@
         <v>2.32</v>
       </c>
       <c r="CB7" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2509,241 +2542,241 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F8">
-        <v>2.68</v>
+        <v>1.73</v>
       </c>
       <c r="G8">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="H8">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="I8">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P8">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2751,241 +2784,241 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F9">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="G9">
         <v>1000</v>
       </c>
       <c r="H9">
+        <v>1.37</v>
+      </c>
+      <c r="I9">
+        <v>1.73</v>
+      </c>
+      <c r="J9">
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <v>12</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>3.55</v>
+      </c>
+      <c r="O9">
+        <v>1.29</v>
+      </c>
+      <c r="P9">
+        <v>1.73</v>
+      </c>
+      <c r="Q9">
+        <v>1.74</v>
+      </c>
+      <c r="R9">
         <v>1.24</v>
       </c>
-      <c r="I9">
-        <v>3.4</v>
-      </c>
-      <c r="J9">
-        <v>3</v>
-      </c>
-      <c r="K9">
-        <v>950</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>1.24</v>
-      </c>
-      <c r="Q9">
-        <v>1.01</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2993,31 +3026,31 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F10">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="G10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="I10">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3026,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3035,10 +3068,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3047,10 +3080,10 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -3059,112 +3092,112 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH10">
         <v>0</v>
@@ -3227,532 +3260,532 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F11">
-        <v>1.3</v>
+        <v>2.76</v>
       </c>
       <c r="G11">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="H11">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>2.6</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F12">
-        <v>1.28</v>
+        <v>2.7</v>
       </c>
       <c r="G12">
-        <v>1.34</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>9.800000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="I12">
-        <v>14</v>
+        <v>3.4</v>
       </c>
       <c r="J12">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P12">
-        <v>3.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q12">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F13">
-        <v>3.95</v>
+        <v>1.3</v>
       </c>
       <c r="G13">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="H13">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="I13">
-        <v>1.91</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3761,10 +3794,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3773,10 +3806,10 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3785,112 +3818,112 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AL13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AU13">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AV13">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AX13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AY13">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AZ13">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BA13">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BB13">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BC13">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BD13">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BE13">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BF13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BG13">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BH13">
         <v>0</v>
@@ -3953,48 +3986,48 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F14">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="G14">
-        <v>2.04</v>
+        <v>970</v>
       </c>
       <c r="H14">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="I14">
-        <v>4.7</v>
+        <v>400</v>
       </c>
       <c r="J14">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4003,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.46</v>
+        <v>1.07</v>
       </c>
       <c r="Q14">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4015,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4027,112 +4060,112 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
         <v>0</v>
@@ -4195,42 +4228,42 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F15">
-        <v>2.42</v>
+        <v>1.28</v>
       </c>
       <c r="G15">
-        <v>2.78</v>
+        <v>1.34</v>
       </c>
       <c r="H15">
-        <v>2.72</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I15">
-        <v>3.15</v>
+        <v>14</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4245,10 +4278,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.99</v>
+        <v>3.25</v>
       </c>
       <c r="Q15">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4437,42 +4470,42 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F16">
-        <v>1.41</v>
+        <v>3.95</v>
       </c>
       <c r="G16">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="H16">
-        <v>3.85</v>
+        <v>1.8</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="J16">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4487,10 +4520,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.07</v>
+        <v>2.62</v>
       </c>
       <c r="Q16">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4499,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4511,112 +4544,112 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH16">
         <v>0</v>
@@ -4679,42 +4712,42 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F17">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>1.94</v>
       </c>
       <c r="H17">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="I17">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J17">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="K17">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4729,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q17">
         <v>1.01</v>
@@ -4921,42 +4954,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F18">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="H18">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="I18">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J18">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K18">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4971,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.07</v>
+        <v>1.99</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5163,48 +5196,48 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F19">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="G19">
-        <v>1.18</v>
+        <v>2.24</v>
       </c>
       <c r="H19">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="I19">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="J19">
-        <v>9.4</v>
+        <v>3.45</v>
       </c>
       <c r="K19">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -5213,10 +5246,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>3.8</v>
+        <v>1.07</v>
       </c>
       <c r="Q19">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5225,10 +5258,10 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5237,112 +5270,112 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
         <v>0</v>
@@ -5405,42 +5438,42 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E20" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F20">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="G20">
-        <v>1.36</v>
+        <v>1000</v>
       </c>
       <c r="H20">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="I20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="J20">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="K20">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5455,10 +5488,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2.38</v>
+        <v>1.07</v>
       </c>
       <c r="Q20">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5647,72 +5680,72 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E21" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="G21">
-        <v>1.66</v>
+        <v>1000</v>
       </c>
       <c r="H21">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="I21">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J21">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="K21">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>2.32</v>
+        <v>1.07</v>
       </c>
       <c r="Q21">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R21">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -5721,417 +5754,1143 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR21">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AS21">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU21">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AV21">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AW21">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AX21">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AY21">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ21">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA21">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BB21">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BC21">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD21">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BE21">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BF21">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BG21">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BH21">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BI21">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BJ21">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK21">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM21">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BN21">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BO21">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BP21">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BQ21">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BR21">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BS21">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT21">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BU21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW21">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY21">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BZ21">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CA21">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E22" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F22">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="G22">
-        <v>1000</v>
+        <v>1.18</v>
       </c>
       <c r="H22">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="I22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="J22">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="K22">
+        <v>10.5</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>3.8</v>
+      </c>
+      <c r="Q22">
+        <v>1.31</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23">
+        <v>1.3</v>
+      </c>
+      <c r="G23">
+        <v>1.36</v>
+      </c>
+      <c r="H23">
+        <v>10.5</v>
+      </c>
+      <c r="I23">
+        <v>15</v>
+      </c>
+      <c r="J23">
+        <v>5.6</v>
+      </c>
+      <c r="K23">
+        <v>6.8</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>2.38</v>
+      </c>
+      <c r="Q23">
+        <v>1.56</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" t="s">
+        <v>162</v>
+      </c>
+      <c r="F24">
+        <v>1.63</v>
+      </c>
+      <c r="G24">
+        <v>1.66</v>
+      </c>
+      <c r="H24">
+        <v>5.7</v>
+      </c>
+      <c r="I24">
+        <v>6.2</v>
+      </c>
+      <c r="J24">
+        <v>4.4</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1.05</v>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>1.23</v>
+      </c>
+      <c r="P24">
+        <v>2.36</v>
+      </c>
+      <c r="Q24">
+        <v>1.68</v>
+      </c>
+      <c r="R24">
+        <v>1.54</v>
+      </c>
+      <c r="S24">
+        <v>2.7</v>
+      </c>
+      <c r="T24">
+        <v>1.76</v>
+      </c>
+      <c r="U24">
+        <v>2.24</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>22</v>
+      </c>
+      <c r="Y24">
+        <v>26</v>
+      </c>
+      <c r="Z24">
+        <v>60</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>10.5</v>
+      </c>
+      <c r="AC24">
+        <v>10.5</v>
+      </c>
+      <c r="AD24">
+        <v>24</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>11</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+      <c r="AH24">
+        <v>20</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>16.5</v>
+      </c>
+      <c r="AK24">
+        <v>16</v>
+      </c>
+      <c r="AL24">
+        <v>50</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>7.6</v>
+      </c>
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>17.5</v>
+      </c>
+      <c r="AQ24">
+        <v>20</v>
+      </c>
+      <c r="AR24">
+        <v>26</v>
+      </c>
+      <c r="AS24">
+        <v>42</v>
+      </c>
+      <c r="AT24">
+        <v>9.4</v>
+      </c>
+      <c r="AU24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV24">
+        <v>16</v>
+      </c>
+      <c r="AW24">
+        <v>32</v>
+      </c>
+      <c r="AX24">
+        <v>9.6</v>
+      </c>
+      <c r="AY24">
+        <v>9</v>
+      </c>
+      <c r="AZ24">
+        <v>16.5</v>
+      </c>
+      <c r="BA24">
+        <v>32</v>
+      </c>
+      <c r="BB24">
+        <v>14</v>
+      </c>
+      <c r="BC24">
+        <v>14</v>
+      </c>
+      <c r="BD24">
+        <v>19.5</v>
+      </c>
+      <c r="BE24">
+        <v>36</v>
+      </c>
+      <c r="BF24">
+        <v>7</v>
+      </c>
+      <c r="BG24">
+        <v>32</v>
+      </c>
+      <c r="BH24">
+        <v>4.1</v>
+      </c>
+      <c r="BI24">
+        <v>3.7</v>
+      </c>
+      <c r="BJ24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK24">
+        <v>6.2</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>13.5</v>
+      </c>
+      <c r="BN24">
+        <v>4.4</v>
+      </c>
+      <c r="BO24">
+        <v>4</v>
+      </c>
+      <c r="BP24">
+        <v>10.5</v>
+      </c>
+      <c r="BQ24">
+        <v>6.4</v>
+      </c>
+      <c r="BR24">
+        <v>23</v>
+      </c>
+      <c r="BS24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT24">
+        <v>9.4</v>
+      </c>
+      <c r="BU24">
+        <v>6</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>11.5</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>11.5</v>
+      </c>
+      <c r="BZ24">
+        <v>15.5</v>
+      </c>
+      <c r="CA24">
+        <v>7.8</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25">
+        <v>1.01</v>
+      </c>
+      <c r="G25">
+        <v>1000</v>
+      </c>
+      <c r="H25">
+        <v>1.01</v>
+      </c>
+      <c r="I25">
+        <v>1000</v>
+      </c>
+      <c r="J25">
+        <v>1.01</v>
+      </c>
+      <c r="K25">
         <v>950</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
         <v>1.07</v>
       </c>
-      <c r="Q22">
-        <v>1.01</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22">
-        <v>0</v>
-      </c>
-      <c r="AI22">
-        <v>0</v>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22">
-        <v>0</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>0</v>
-      </c>
-      <c r="AO22">
-        <v>0</v>
-      </c>
-      <c r="AP22">
-        <v>0</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22">
-        <v>0</v>
-      </c>
-      <c r="AV22">
-        <v>0</v>
-      </c>
-      <c r="AW22">
-        <v>0</v>
-      </c>
-      <c r="AX22">
-        <v>0</v>
-      </c>
-      <c r="AY22">
-        <v>0</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>0</v>
-      </c>
-      <c r="BC22">
-        <v>0</v>
-      </c>
-      <c r="BD22">
-        <v>0</v>
-      </c>
-      <c r="BE22">
-        <v>0</v>
-      </c>
-      <c r="BF22">
-        <v>0</v>
-      </c>
-      <c r="BG22">
-        <v>0</v>
-      </c>
-      <c r="BH22">
-        <v>0</v>
-      </c>
-      <c r="BI22">
-        <v>0</v>
-      </c>
-      <c r="BJ22">
-        <v>0</v>
-      </c>
-      <c r="BK22">
-        <v>0</v>
-      </c>
-      <c r="BL22">
-        <v>0</v>
-      </c>
-      <c r="BM22">
-        <v>0</v>
-      </c>
-      <c r="BN22">
-        <v>0</v>
-      </c>
-      <c r="BO22">
-        <v>0</v>
-      </c>
-      <c r="BP22">
-        <v>0</v>
-      </c>
-      <c r="BQ22">
-        <v>0</v>
-      </c>
-      <c r="BR22">
-        <v>0</v>
-      </c>
-      <c r="BS22">
-        <v>0</v>
-      </c>
-      <c r="BT22">
-        <v>0</v>
-      </c>
-      <c r="BU22">
-        <v>0</v>
-      </c>
-      <c r="BV22">
-        <v>0</v>
-      </c>
-      <c r="BW22">
-        <v>0</v>
-      </c>
-      <c r="BX22">
-        <v>0</v>
-      </c>
-      <c r="BY22">
-        <v>0</v>
-      </c>
-      <c r="BZ22">
-        <v>0</v>
-      </c>
-      <c r="CA22">
-        <v>0</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>153</v>
+      <c r="Q25">
+        <v>1.01</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="200">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Japanese J League</t>
   </si>
   <si>
+    <t>Armenian Premier League</t>
+  </si>
+  <si>
     <t>Indonesian Super League</t>
   </si>
   <si>
@@ -286,15 +289,27 @@
     <t>Latvian Virsliga</t>
   </si>
   <si>
-    <t>Armenian Premier League</t>
+    <t>Czech 2 Liga</t>
+  </si>
+  <si>
+    <t>Romanian Liga I</t>
   </si>
   <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Danish 1st Division</t>
+  </si>
+  <si>
     <t>Qatari Stars League</t>
   </si>
   <si>
+    <t>German Bundesliga 2</t>
+  </si>
+  <si>
     <t>Serbian Super League</t>
   </si>
   <si>
@@ -346,6 +361,9 @@
     <t>15:45:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>16:15:00</t>
   </si>
   <si>
@@ -358,6 +376,9 @@
     <t>18:00:00</t>
   </si>
   <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -382,6 +403,9 @@
     <t>Kyoto</t>
   </si>
   <si>
+    <t>FC Van Yerevan</t>
+  </si>
+  <si>
     <t>Dewa United FC</t>
   </si>
   <si>
@@ -397,10 +421,16 @@
     <t>Ogre United</t>
   </si>
   <si>
+    <t>Ararat Armenia</t>
+  </si>
+  <si>
+    <t>Trinec</t>
+  </si>
+  <si>
     <t>FK Riga</t>
   </si>
   <si>
-    <t>Ararat Armenia</t>
+    <t>Farul Constanta</t>
   </si>
   <si>
     <t>Al-Quadisiya (KSA)</t>
@@ -409,15 +439,42 @@
     <t>Al Faisaly ( KSA )</t>
   </si>
   <si>
+    <t>Rakow Czestochowa</t>
+  </si>
+  <si>
+    <t>Hobro</t>
+  </si>
+  <si>
+    <t>Usti nad Labem</t>
+  </si>
+  <si>
+    <t>Dukla Prague</t>
+  </si>
+  <si>
+    <t>MAS Taborsko</t>
+  </si>
+  <si>
+    <t>FK Pribram</t>
+  </si>
+  <si>
     <t>Al Rayyan</t>
   </si>
   <si>
     <t>Al Wahda (Abu Dhabi)</t>
   </si>
   <si>
+    <t>SV Darmstadt</t>
+  </si>
+  <si>
+    <t>Nurnberg</t>
+  </si>
+  <si>
     <t>Zeleznicar Pancevo</t>
   </si>
   <si>
+    <t>Vendsyssel FF</t>
+  </si>
+  <si>
     <t>Lunds BK</t>
   </si>
   <si>
@@ -427,9 +484,15 @@
     <t>AZ Alkmaar</t>
   </si>
   <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
     <t>Al Ahli</t>
   </si>
   <si>
+    <t>Wisla Krakow</t>
+  </si>
+  <si>
     <t>West Ham</t>
   </si>
   <si>
@@ -454,6 +517,9 @@
     <t>Kashiwa</t>
   </si>
   <si>
+    <t>BKMA Yerevan</t>
+  </si>
+  <si>
     <t>Bhayangkara FC</t>
   </si>
   <si>
@@ -469,10 +535,16 @@
     <t>Liepajas Metalurgs</t>
   </si>
   <si>
+    <t>FC Syunik</t>
+  </si>
+  <si>
+    <t>MFK Karvina</t>
+  </si>
+  <si>
     <t>FK Auda</t>
   </si>
   <si>
-    <t>FC Syunik</t>
+    <t>UTA Arad</t>
   </si>
   <si>
     <t>Al-Ettifaq</t>
@@ -481,15 +553,42 @@
     <t>Al-Ittihad</t>
   </si>
   <si>
+    <t>LKP Motor Lublin</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>Vysocina Jihlava</t>
+  </si>
+  <si>
+    <t>FC Sellier &amp; Bellot Vlasim</t>
+  </si>
+  <si>
+    <t>SK Kladno</t>
+  </si>
+  <si>
+    <t>Banik Ostrava B</t>
+  </si>
+  <si>
     <t>Al Ahli (QAT)</t>
   </si>
   <si>
     <t>Al Sharjah</t>
   </si>
   <si>
+    <t>Arminia Bielefeld</t>
+  </si>
+  <si>
+    <t>Hannover</t>
+  </si>
+  <si>
     <t>Macva Sabac</t>
   </si>
   <si>
+    <t>Aarhus Fremad</t>
+  </si>
+  <si>
     <t>Rosengard</t>
   </si>
   <si>
@@ -499,16 +598,22 @@
     <t>Willem II</t>
   </si>
   <si>
+    <t>Dinamo Bucharest</t>
+  </si>
+  <si>
     <t>Al-Hazm (KSA)</t>
   </si>
   <si>
+    <t>Jagiellonia Bialystock</t>
+  </si>
+  <si>
     <t>Wrexham</t>
   </si>
   <si>
     <t>ES Setif</t>
   </si>
   <si>
-    <t>2026-09-09 11:33:30</t>
+    <t>2026-09-09 13:48:23</t>
   </si>
 </sst>
 </file>
@@ -840,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1090,16 +1195,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="F2">
         <v>1.2</v>
@@ -1108,46 +1213,46 @@
         <v>1.22</v>
       </c>
       <c r="H2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="K2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="L2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R2">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="S2">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="T2">
         <v>2.22</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
         <v>1.05</v>
@@ -1177,10 +1282,10 @@
         <v>70</v>
       </c>
       <c r="AE2">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2">
         <v>15.5</v>
@@ -1189,7 +1294,7 @@
         <v>42</v>
       </c>
       <c r="AI2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AJ2">
         <v>10</v>
@@ -1198,22 +1303,22 @@
         <v>14</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN2">
         <v>3.2</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP2">
         <v>6.8</v>
       </c>
       <c r="AQ2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR2">
         <v>7.6</v>
@@ -1222,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="AT2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
         <v>19</v>
@@ -1237,7 +1342,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
         <v>6.8</v>
@@ -1255,37 +1360,37 @@
         <v>7</v>
       </c>
       <c r="BE2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF2">
         <v>2.88</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BO2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP2">
         <v>6.4</v>
@@ -1309,22 +1414,22 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CA2">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1332,22 +1437,22 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="F3">
         <v>2.78</v>
       </c>
       <c r="G3">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H3">
         <v>2.94</v>
@@ -1365,10 +1470,10 @@
         <v>1.51</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
         <v>1.45</v>
@@ -1386,7 +1491,7 @@
         <v>4.5</v>
       </c>
       <c r="T3">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U3">
         <v>1.94</v>
@@ -1398,7 +1503,7 @@
         <v>1.52</v>
       </c>
       <c r="X3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
         <v>11</v>
@@ -1419,7 +1524,7 @@
         <v>14</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF3">
         <v>17</v>
@@ -1497,7 +1602,7 @@
         <v>46</v>
       </c>
       <c r="BE3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
         <v>27</v>
@@ -1506,7 +1611,7 @@
         <v>28</v>
       </c>
       <c r="BH3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI3">
         <v>2.38</v>
@@ -1527,7 +1632,7 @@
         <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP3">
         <v>28</v>
@@ -1566,7 +1671,7 @@
         <v>4.7</v>
       </c>
       <c r="CB3" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1574,34 +1679,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="F4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G4">
         <v>1.85</v>
       </c>
       <c r="H4">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
         <v>3.55</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1619,7 +1724,7 @@
         <v>1.74</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R4">
         <v>1.27</v>
@@ -1808,7 +1913,7 @@
         <v>4.2</v>
       </c>
       <c r="CB4" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1816,25 +1921,25 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="F5">
         <v>2.18</v>
       </c>
       <c r="G5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I5">
         <v>3.55</v>
@@ -1855,7 +1960,7 @@
         <v>4.3</v>
       </c>
       <c r="O5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
         <v>2.14</v>
@@ -1870,7 +1975,7 @@
         <v>3</v>
       </c>
       <c r="T5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U5">
         <v>2.3</v>
@@ -1879,13 +1984,13 @@
         <v>1.39</v>
       </c>
       <c r="W5">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X5">
         <v>18.5</v>
       </c>
       <c r="Y5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z5">
         <v>32</v>
@@ -1939,13 +2044,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR5">
         <v>21</v>
       </c>
       <c r="AS5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT5">
         <v>9.800000000000001</v>
@@ -1957,7 +2062,7 @@
         <v>13</v>
       </c>
       <c r="AW5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
         <v>13.5</v>
@@ -1969,25 +2074,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC5">
         <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF5">
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH5">
         <v>5</v>
@@ -2050,7 +2155,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2058,28 +2163,28 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="F6">
         <v>3.1</v>
       </c>
       <c r="G6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I6">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J6">
         <v>3.25</v>
@@ -2121,115 +2226,115 @@
         <v>1.61</v>
       </c>
       <c r="W6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB6">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC6">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG6">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP6">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6">
+        <v>8.4</v>
+      </c>
+      <c r="AR6">
+        <v>14</v>
+      </c>
+      <c r="AS6">
+        <v>26</v>
+      </c>
+      <c r="AT6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU6">
         <v>6.8</v>
       </c>
-      <c r="AR6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS6">
-        <v>1.46</v>
-      </c>
-      <c r="AT6">
-        <v>7.6</v>
-      </c>
-      <c r="AU6">
-        <v>5.6</v>
-      </c>
       <c r="AV6">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>1.46</v>
+        <v>21</v>
       </c>
       <c r="AX6">
-        <v>1.46</v>
+        <v>18.5</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AZ6">
+        <v>16.5</v>
+      </c>
+      <c r="BA6">
         <v>11.5</v>
       </c>
-      <c r="BA6">
-        <v>1.46</v>
-      </c>
       <c r="BB6">
-        <v>1.46</v>
+        <v>12</v>
       </c>
       <c r="BC6">
-        <v>1.46</v>
+        <v>11</v>
       </c>
       <c r="BD6">
-        <v>1.46</v>
+        <v>12</v>
       </c>
       <c r="BE6">
-        <v>1.46</v>
+        <v>14</v>
       </c>
       <c r="BF6">
-        <v>1.46</v>
+        <v>11</v>
       </c>
       <c r="BG6">
-        <v>1.46</v>
+        <v>18</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2292,7 +2397,7 @@
         <v>1.33</v>
       </c>
       <c r="CB6" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2300,16 +2405,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="F7">
         <v>4.2</v>
@@ -2375,7 +2480,7 @@
         <v>13</v>
       </c>
       <c r="AA7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB7">
         <v>18</v>
@@ -2390,7 +2495,7 @@
         <v>20</v>
       </c>
       <c r="AF7">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AG7">
         <v>18.5</v>
@@ -2417,7 +2522,7 @@
         <v>60</v>
       </c>
       <c r="AO7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP7">
         <v>14.5</v>
@@ -2432,19 +2537,19 @@
         <v>18</v>
       </c>
       <c r="AT7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU7">
         <v>8</v>
       </c>
       <c r="AV7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7">
         <v>16</v>
       </c>
       <c r="AX7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY7">
         <v>15</v>
@@ -2453,25 +2558,25 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB7">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BD7">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE7">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF7">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2534,7 +2639,7 @@
         <v>2.32</v>
       </c>
       <c r="CB7" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2542,34 +2647,34 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="F8">
-        <v>1.73</v>
+        <v>3.15</v>
       </c>
       <c r="G8">
-        <v>1.92</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="I8">
-        <v>6.8</v>
+        <v>2.34</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2578,22 +2683,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.75</v>
+        <v>3.55</v>
       </c>
       <c r="O8">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q8">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="R8">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="S8">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2602,10 +2707,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2776,7 +2881,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2784,58 +2889,58 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="F9">
-        <v>5.4</v>
+        <v>1.73</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>1.92</v>
       </c>
       <c r="H9">
-        <v>1.37</v>
+        <v>4.1</v>
       </c>
       <c r="I9">
-        <v>1.73</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K9">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.55</v>
+        <v>1.89</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P9">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="Q9">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2844,7 +2949,7 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
         <v>1.01</v>
@@ -3018,7 +3123,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3026,241 +3131,241 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F10">
-        <v>1.85</v>
+        <v>5.7</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="H10">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>1.7</v>
       </c>
       <c r="J10">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P10">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3268,241 +3373,241 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="F11">
-        <v>2.76</v>
+        <v>1.85</v>
       </c>
       <c r="G11">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="H11">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="I11">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q11">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="R11">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BG11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3510,34 +3615,34 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="F12">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H12">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="I12">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3546,34 +3651,34 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>5.7</v>
       </c>
       <c r="O12">
         <v>1.15</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
-        <v>1.06</v>
+        <v>1.63</v>
       </c>
       <c r="S12">
-        <v>1.15</v>
+        <v>2.12</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3633,22 +3738,22 @@
         <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
         <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
         <v>1.03</v>
@@ -3657,10 +3762,10 @@
         <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
         <v>1.03</v>
@@ -3744,36 +3849,36 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="F13">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="G13">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J13">
         <v>3</v>
@@ -3782,270 +3887,270 @@
         <v>950</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="F14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="G14">
-        <v>970</v>
+        <v>1.61</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="I14">
         <v>400</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="K14">
         <v>950</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P14">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4054,10 +4159,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4168,67 +4273,67 @@
         <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4236,483 +4341,483 @@
         <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="F15">
-        <v>1.28</v>
+        <v>4.6</v>
       </c>
       <c r="G15">
-        <v>1.34</v>
+        <v>15</v>
       </c>
       <c r="H15">
-        <v>9.800000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="I15">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="J15">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="K15">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P15">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q15">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="F16">
-        <v>3.95</v>
+        <v>1.3</v>
       </c>
       <c r="G16">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="H16">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="I16">
-        <v>1.91</v>
+        <v>1000</v>
       </c>
       <c r="J16">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>1.51</v>
+        <v>1.17</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T16">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4720,483 +4825,483 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="F17">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="G17">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="H17">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="I17">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="J17">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="K17">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P17">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="F18">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="G18">
-        <v>2.78</v>
+        <v>1.34</v>
       </c>
       <c r="H18">
-        <v>2.74</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I18">
-        <v>3.35</v>
+        <v>13.5</v>
       </c>
       <c r="J18">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="K18">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P18">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CB18" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5204,241 +5309,241 @@
         <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="F19">
-        <v>1.43</v>
+        <v>3.95</v>
       </c>
       <c r="G19">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="H19">
-        <v>3.85</v>
+        <v>1.77</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>1.94</v>
       </c>
       <c r="J19">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="K19">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M19">
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P19">
-        <v>1.07</v>
+        <v>2.62</v>
       </c>
       <c r="Q19">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5446,725 +5551,725 @@
         <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E20" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="F20">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="G20">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="H20">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="I20">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J20">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K20">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
-        <v>1.07</v>
+        <v>2.48</v>
       </c>
       <c r="Q20">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="F21">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="H21">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="I21">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="J21">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P21">
-        <v>1.07</v>
+        <v>2.34</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="F22">
-        <v>1.17</v>
+        <v>1.97</v>
       </c>
       <c r="G22">
-        <v>1.18</v>
+        <v>2.24</v>
       </c>
       <c r="H22">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="I22">
-        <v>28</v>
+        <v>4.8</v>
       </c>
       <c r="J22">
-        <v>9.4</v>
+        <v>3.5</v>
       </c>
       <c r="K22">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P22">
-        <v>3.8</v>
+        <v>1.98</v>
       </c>
       <c r="Q22">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6172,725 +6277,4113 @@
         <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="F23">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="G23">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="H23">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="I23">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J23">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="K23">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P23">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="Q23">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="F24">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="G24">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="H24">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="I24">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="K24">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="O24">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P24">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="Q24">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="R24">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="S24">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="T24">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X24">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
         <v>1000</v>
       </c>
       <c r="AF24">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
         <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
         <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="F25">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="G25">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H25">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="I25">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J25">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K25">
+        <v>4.1</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>2.9</v>
+      </c>
+      <c r="O25">
+        <v>1.22</v>
+      </c>
+      <c r="P25">
+        <v>2</v>
+      </c>
+      <c r="Q25">
+        <v>1.43</v>
+      </c>
+      <c r="R25">
+        <v>1.34</v>
+      </c>
+      <c r="S25">
+        <v>2.24</v>
+      </c>
+      <c r="T25">
+        <v>1.01</v>
+      </c>
+      <c r="U25">
+        <v>1.01</v>
+      </c>
+      <c r="V25">
+        <v>1.46</v>
+      </c>
+      <c r="W25">
+        <v>1.58</v>
+      </c>
+      <c r="X25">
+        <v>1000</v>
+      </c>
+      <c r="Y25">
+        <v>1000</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>1000</v>
+      </c>
+      <c r="AC25">
+        <v>1000</v>
+      </c>
+      <c r="AD25">
+        <v>1000</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>1000</v>
+      </c>
+      <c r="AG25">
+        <v>1000</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25">
+        <v>1.03</v>
+      </c>
+      <c r="AR25">
+        <v>1.03</v>
+      </c>
+      <c r="AS25">
+        <v>1.03</v>
+      </c>
+      <c r="AT25">
+        <v>1.03</v>
+      </c>
+      <c r="AU25">
+        <v>1.03</v>
+      </c>
+      <c r="AV25">
+        <v>1.03</v>
+      </c>
+      <c r="AW25">
+        <v>1.03</v>
+      </c>
+      <c r="AX25">
+        <v>1.03</v>
+      </c>
+      <c r="AY25">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25">
+        <v>1.03</v>
+      </c>
+      <c r="BA25">
+        <v>1.03</v>
+      </c>
+      <c r="BB25">
+        <v>1.03</v>
+      </c>
+      <c r="BC25">
+        <v>1.03</v>
+      </c>
+      <c r="BD25">
+        <v>1.03</v>
+      </c>
+      <c r="BE25">
+        <v>1.03</v>
+      </c>
+      <c r="BF25">
+        <v>1.01</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.01</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.01</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s">
+        <v>147</v>
+      </c>
+      <c r="E26" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26">
+        <v>1.79</v>
+      </c>
+      <c r="G26">
+        <v>1.91</v>
+      </c>
+      <c r="H26">
+        <v>4</v>
+      </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
+      <c r="J26">
+        <v>4.2</v>
+      </c>
+      <c r="K26">
+        <v>4.9</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>5.7</v>
+      </c>
+      <c r="O26">
+        <v>1.14</v>
+      </c>
+      <c r="P26">
+        <v>2.5</v>
+      </c>
+      <c r="Q26">
+        <v>1.38</v>
+      </c>
+      <c r="R26">
+        <v>1.66</v>
+      </c>
+      <c r="S26">
+        <v>2.08</v>
+      </c>
+      <c r="T26">
+        <v>1.47</v>
+      </c>
+      <c r="U26">
+        <v>2.48</v>
+      </c>
+      <c r="V26">
+        <v>1.25</v>
+      </c>
+      <c r="W26">
+        <v>2.08</v>
+      </c>
+      <c r="X26">
+        <v>1000</v>
+      </c>
+      <c r="Y26">
+        <v>1000</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>25</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>1000</v>
+      </c>
+      <c r="AG26">
+        <v>23</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>11</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26">
+        <v>1.01</v>
+      </c>
+      <c r="AR26">
+        <v>1.01</v>
+      </c>
+      <c r="AS26">
+        <v>1.01</v>
+      </c>
+      <c r="AT26">
+        <v>8</v>
+      </c>
+      <c r="AU26">
+        <v>6.4</v>
+      </c>
+      <c r="AV26">
+        <v>9.6</v>
+      </c>
+      <c r="AW26">
+        <v>1.01</v>
+      </c>
+      <c r="AX26">
+        <v>7.8</v>
+      </c>
+      <c r="AY26">
+        <v>6.2</v>
+      </c>
+      <c r="AZ26">
+        <v>8.4</v>
+      </c>
+      <c r="BA26">
+        <v>1.01</v>
+      </c>
+      <c r="BB26">
+        <v>1.01</v>
+      </c>
+      <c r="BC26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD26">
+        <v>1.01</v>
+      </c>
+      <c r="BE26">
+        <v>1.01</v>
+      </c>
+      <c r="BF26">
+        <v>4.4</v>
+      </c>
+      <c r="BG26">
+        <v>1.01</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>1.01</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
+        <v>1.01</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>1.01</v>
+      </c>
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
+        <v>1.01</v>
+      </c>
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
+        <v>1.01</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>1.01</v>
+      </c>
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
+        <v>1.01</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>1.01</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
+        <v>1.01</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" t="s">
+        <v>186</v>
+      </c>
+      <c r="F27">
+        <v>2.44</v>
+      </c>
+      <c r="G27">
+        <v>2.78</v>
+      </c>
+      <c r="H27">
+        <v>2.74</v>
+      </c>
+      <c r="I27">
+        <v>3.15</v>
+      </c>
+      <c r="J27">
+        <v>3.35</v>
+      </c>
+      <c r="K27">
+        <v>4.5</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
+        <v>1.99</v>
+      </c>
+      <c r="O27">
+        <v>1.26</v>
+      </c>
+      <c r="P27">
+        <v>1.99</v>
+      </c>
+      <c r="Q27">
+        <v>1.8</v>
+      </c>
+      <c r="R27">
+        <v>1.08</v>
+      </c>
+      <c r="S27">
+        <v>1.01</v>
+      </c>
+      <c r="T27">
+        <v>1.01</v>
+      </c>
+      <c r="U27">
+        <v>1.01</v>
+      </c>
+      <c r="V27">
+        <v>1.01</v>
+      </c>
+      <c r="W27">
+        <v>1.01</v>
+      </c>
+      <c r="X27">
+        <v>1000</v>
+      </c>
+      <c r="Y27">
+        <v>1000</v>
+      </c>
+      <c r="Z27">
+        <v>1000</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>1000</v>
+      </c>
+      <c r="AC27">
+        <v>1000</v>
+      </c>
+      <c r="AD27">
+        <v>1000</v>
+      </c>
+      <c r="AE27">
+        <v>1000</v>
+      </c>
+      <c r="AF27">
+        <v>1000</v>
+      </c>
+      <c r="AG27">
+        <v>1000</v>
+      </c>
+      <c r="AH27">
+        <v>1000</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>1000</v>
+      </c>
+      <c r="AK27">
+        <v>1000</v>
+      </c>
+      <c r="AL27">
+        <v>1000</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>1000</v>
+      </c>
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27">
+        <v>1.01</v>
+      </c>
+      <c r="AR27">
+        <v>1.01</v>
+      </c>
+      <c r="AS27">
+        <v>1.01</v>
+      </c>
+      <c r="AT27">
+        <v>1.01</v>
+      </c>
+      <c r="AU27">
+        <v>1.01</v>
+      </c>
+      <c r="AV27">
+        <v>1.01</v>
+      </c>
+      <c r="AW27">
+        <v>1.01</v>
+      </c>
+      <c r="AX27">
+        <v>1.01</v>
+      </c>
+      <c r="AY27">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27">
+        <v>1.01</v>
+      </c>
+      <c r="BA27">
+        <v>1.01</v>
+      </c>
+      <c r="BB27">
+        <v>1.01</v>
+      </c>
+      <c r="BC27">
+        <v>1.01</v>
+      </c>
+      <c r="BD27">
+        <v>1.01</v>
+      </c>
+      <c r="BE27">
+        <v>1.01</v>
+      </c>
+      <c r="BF27">
+        <v>1.01</v>
+      </c>
+      <c r="BG27">
+        <v>1.01</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.01</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.01</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.01</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.01</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28">
+        <v>2.74</v>
+      </c>
+      <c r="G28">
+        <v>3.05</v>
+      </c>
+      <c r="H28">
+        <v>2.38</v>
+      </c>
+      <c r="I28">
+        <v>2.56</v>
+      </c>
+      <c r="J28">
+        <v>3.85</v>
+      </c>
+      <c r="K28">
+        <v>4.2</v>
+      </c>
+      <c r="L28">
+        <v>1.31</v>
+      </c>
+      <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
+      <c r="O28">
+        <v>1.18</v>
+      </c>
+      <c r="P28">
+        <v>2.42</v>
+      </c>
+      <c r="Q28">
+        <v>1.54</v>
+      </c>
+      <c r="R28">
+        <v>1.52</v>
+      </c>
+      <c r="S28">
+        <v>2.48</v>
+      </c>
+      <c r="T28">
+        <v>1.49</v>
+      </c>
+      <c r="U28">
+        <v>2.44</v>
+      </c>
+      <c r="V28">
+        <v>1.64</v>
+      </c>
+      <c r="W28">
+        <v>1.48</v>
+      </c>
+      <c r="X28">
+        <v>1000</v>
+      </c>
+      <c r="Y28">
+        <v>20</v>
+      </c>
+      <c r="Z28">
+        <v>25</v>
+      </c>
+      <c r="AA28">
+        <v>46</v>
+      </c>
+      <c r="AB28">
+        <v>22</v>
+      </c>
+      <c r="AC28">
+        <v>11.5</v>
+      </c>
+      <c r="AD28">
+        <v>15</v>
+      </c>
+      <c r="AE28">
+        <v>30</v>
+      </c>
+      <c r="AF28">
+        <v>30</v>
+      </c>
+      <c r="AG28">
+        <v>17.5</v>
+      </c>
+      <c r="AH28">
+        <v>20</v>
+      </c>
+      <c r="AI28">
+        <v>38</v>
+      </c>
+      <c r="AJ28">
+        <v>60</v>
+      </c>
+      <c r="AK28">
+        <v>38</v>
+      </c>
+      <c r="AL28">
+        <v>44</v>
+      </c>
+      <c r="AM28">
+        <v>85</v>
+      </c>
+      <c r="AN28">
+        <v>23</v>
+      </c>
+      <c r="AO28">
+        <v>18.5</v>
+      </c>
+      <c r="AP28">
+        <v>3.15</v>
+      </c>
+      <c r="AQ28">
+        <v>11</v>
+      </c>
+      <c r="AR28">
+        <v>14</v>
+      </c>
+      <c r="AS28">
+        <v>2.96</v>
+      </c>
+      <c r="AT28">
+        <v>12</v>
+      </c>
+      <c r="AU28">
+        <v>7.2</v>
+      </c>
+      <c r="AV28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW28">
+        <v>2.86</v>
+      </c>
+      <c r="AX28">
+        <v>2.86</v>
+      </c>
+      <c r="AY28">
+        <v>9.6</v>
+      </c>
+      <c r="AZ28">
+        <v>11</v>
+      </c>
+      <c r="BA28">
+        <v>2.92</v>
+      </c>
+      <c r="BB28">
+        <v>3</v>
+      </c>
+      <c r="BC28">
+        <v>17.5</v>
+      </c>
+      <c r="BD28">
+        <v>2.96</v>
+      </c>
+      <c r="BE28">
+        <v>3.05</v>
+      </c>
+      <c r="BF28">
+        <v>13</v>
+      </c>
+      <c r="BG28">
+        <v>10</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>3.55</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>6.2</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.01</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>5</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>11.5</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.01</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>4.5</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>8.4</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>188</v>
+      </c>
+      <c r="F29">
+        <v>2.6</v>
+      </c>
+      <c r="G29">
+        <v>2.76</v>
+      </c>
+      <c r="H29">
+        <v>2.6</v>
+      </c>
+      <c r="I29">
+        <v>2.68</v>
+      </c>
+      <c r="J29">
+        <v>3.95</v>
+      </c>
+      <c r="K29">
+        <v>4.1</v>
+      </c>
+      <c r="L29">
+        <v>1.26</v>
+      </c>
+      <c r="M29">
+        <v>1.01</v>
+      </c>
+      <c r="N29">
+        <v>5.6</v>
+      </c>
+      <c r="O29">
+        <v>1.16</v>
+      </c>
+      <c r="P29">
+        <v>2.8</v>
+      </c>
+      <c r="Q29">
+        <v>1.47</v>
+      </c>
+      <c r="R29">
+        <v>1.74</v>
+      </c>
+      <c r="S29">
+        <v>2.08</v>
+      </c>
+      <c r="T29">
+        <v>1.41</v>
+      </c>
+      <c r="U29">
+        <v>2.7</v>
+      </c>
+      <c r="V29">
+        <v>1.59</v>
+      </c>
+      <c r="W29">
+        <v>1.56</v>
+      </c>
+      <c r="X29">
+        <v>40</v>
+      </c>
+      <c r="Y29">
+        <v>22</v>
+      </c>
+      <c r="Z29">
+        <v>26</v>
+      </c>
+      <c r="AA29">
+        <v>42</v>
+      </c>
+      <c r="AB29">
+        <v>23</v>
+      </c>
+      <c r="AC29">
+        <v>12.5</v>
+      </c>
+      <c r="AD29">
+        <v>15.5</v>
+      </c>
+      <c r="AE29">
+        <v>28</v>
+      </c>
+      <c r="AF29">
+        <v>28</v>
+      </c>
+      <c r="AG29">
+        <v>15.5</v>
+      </c>
+      <c r="AH29">
+        <v>16.5</v>
+      </c>
+      <c r="AI29">
+        <v>30</v>
+      </c>
+      <c r="AJ29">
+        <v>44</v>
+      </c>
+      <c r="AK29">
+        <v>29</v>
+      </c>
+      <c r="AL29">
+        <v>32</v>
+      </c>
+      <c r="AM29">
+        <v>55</v>
+      </c>
+      <c r="AN29">
+        <v>15.5</v>
+      </c>
+      <c r="AO29">
+        <v>14.5</v>
+      </c>
+      <c r="AP29">
+        <v>4.2</v>
+      </c>
+      <c r="AQ29">
+        <v>14.5</v>
+      </c>
+      <c r="AR29">
+        <v>4</v>
+      </c>
+      <c r="AS29">
+        <v>4.2</v>
+      </c>
+      <c r="AT29">
+        <v>15</v>
+      </c>
+      <c r="AU29">
+        <v>9</v>
+      </c>
+      <c r="AV29">
+        <v>9.6</v>
+      </c>
+      <c r="AW29">
+        <v>4</v>
+      </c>
+      <c r="AX29">
+        <v>18.5</v>
+      </c>
+      <c r="AY29">
+        <v>10</v>
+      </c>
+      <c r="AZ29">
+        <v>10.5</v>
+      </c>
+      <c r="BA29">
+        <v>4.1</v>
+      </c>
+      <c r="BB29">
+        <v>4.3</v>
+      </c>
+      <c r="BC29">
+        <v>19</v>
+      </c>
+      <c r="BD29">
+        <v>4.1</v>
+      </c>
+      <c r="BE29">
+        <v>4.3</v>
+      </c>
+      <c r="BF29">
+        <v>9.6</v>
+      </c>
+      <c r="BG29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>3.7</v>
+      </c>
+      <c r="BJ29">
+        <v>12</v>
+      </c>
+      <c r="BK29">
+        <v>6.2</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>21</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>4.9</v>
+      </c>
+      <c r="BP29">
+        <v>25</v>
+      </c>
+      <c r="BQ29">
+        <v>10.5</v>
+      </c>
+      <c r="BR29">
+        <v>34</v>
+      </c>
+      <c r="BS29">
+        <v>14</v>
+      </c>
+      <c r="BT29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU29">
+        <v>4.8</v>
+      </c>
+      <c r="BV29">
+        <v>24</v>
+      </c>
+      <c r="BW29">
+        <v>10</v>
+      </c>
+      <c r="BX29">
+        <v>32</v>
+      </c>
+      <c r="BY29">
+        <v>13.5</v>
+      </c>
+      <c r="BZ29">
+        <v>20</v>
+      </c>
+      <c r="CA29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30">
+        <v>1.45</v>
+      </c>
+      <c r="G30">
+        <v>1.57</v>
+      </c>
+      <c r="H30">
+        <v>7.2</v>
+      </c>
+      <c r="I30">
+        <v>110</v>
+      </c>
+      <c r="J30">
+        <v>4.4</v>
+      </c>
+      <c r="K30">
+        <v>11</v>
+      </c>
+      <c r="L30">
+        <v>1.01</v>
+      </c>
+      <c r="M30">
+        <v>1.01</v>
+      </c>
+      <c r="N30">
+        <v>1.01</v>
+      </c>
+      <c r="O30">
+        <v>1.23</v>
+      </c>
+      <c r="P30">
+        <v>1.89</v>
+      </c>
+      <c r="Q30">
+        <v>1.81</v>
+      </c>
+      <c r="R30">
+        <v>1.25</v>
+      </c>
+      <c r="S30">
+        <v>2.48</v>
+      </c>
+      <c r="T30">
+        <v>1.01</v>
+      </c>
+      <c r="U30">
+        <v>1.01</v>
+      </c>
+      <c r="V30">
+        <v>1.09</v>
+      </c>
+      <c r="W30">
+        <v>2.76</v>
+      </c>
+      <c r="X30">
+        <v>1000</v>
+      </c>
+      <c r="Y30">
+        <v>1000</v>
+      </c>
+      <c r="Z30">
+        <v>1000</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>1000</v>
+      </c>
+      <c r="AC30">
+        <v>1000</v>
+      </c>
+      <c r="AD30">
+        <v>1000</v>
+      </c>
+      <c r="AE30">
+        <v>1000</v>
+      </c>
+      <c r="AF30">
+        <v>1000</v>
+      </c>
+      <c r="AG30">
+        <v>1000</v>
+      </c>
+      <c r="AH30">
+        <v>1000</v>
+      </c>
+      <c r="AI30">
+        <v>1000</v>
+      </c>
+      <c r="AJ30">
+        <v>1000</v>
+      </c>
+      <c r="AK30">
+        <v>1000</v>
+      </c>
+      <c r="AL30">
+        <v>1000</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>1000</v>
+      </c>
+      <c r="AO30">
+        <v>1000</v>
+      </c>
+      <c r="AP30">
+        <v>1.03</v>
+      </c>
+      <c r="AQ30">
+        <v>1.03</v>
+      </c>
+      <c r="AR30">
+        <v>1.03</v>
+      </c>
+      <c r="AS30">
+        <v>1.03</v>
+      </c>
+      <c r="AT30">
+        <v>1.03</v>
+      </c>
+      <c r="AU30">
+        <v>1.03</v>
+      </c>
+      <c r="AV30">
+        <v>1.03</v>
+      </c>
+      <c r="AW30">
+        <v>1.03</v>
+      </c>
+      <c r="AX30">
+        <v>1.03</v>
+      </c>
+      <c r="AY30">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30">
+        <v>1.03</v>
+      </c>
+      <c r="BA30">
+        <v>1.03</v>
+      </c>
+      <c r="BB30">
+        <v>1.03</v>
+      </c>
+      <c r="BC30">
+        <v>1.03</v>
+      </c>
+      <c r="BD30">
+        <v>1.03</v>
+      </c>
+      <c r="BE30">
+        <v>1.03</v>
+      </c>
+      <c r="BF30">
+        <v>1.01</v>
+      </c>
+      <c r="BG30">
+        <v>1.01</v>
+      </c>
+      <c r="BH30">
+        <v>4.7</v>
+      </c>
+      <c r="BI30">
+        <v>2.74</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>1.01</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.01</v>
+      </c>
+      <c r="BN30">
+        <v>1000</v>
+      </c>
+      <c r="BO30">
+        <v>3.3</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>1.01</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.01</v>
+      </c>
+      <c r="BT30">
+        <v>1000</v>
+      </c>
+      <c r="BU30">
+        <v>1.01</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.01</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>1.01</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E31" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31">
+        <v>2.6</v>
+      </c>
+      <c r="G31">
+        <v>3.05</v>
+      </c>
+      <c r="H31">
+        <v>2.26</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>3.25</v>
+      </c>
+      <c r="K31">
+        <v>4.4</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>2</v>
+      </c>
+      <c r="Q31">
+        <v>1.81</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <v>0</v>
+      </c>
+      <c r="AV31">
+        <v>0</v>
+      </c>
+      <c r="AW31">
+        <v>0</v>
+      </c>
+      <c r="AX31">
+        <v>0</v>
+      </c>
+      <c r="AY31">
+        <v>0</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31">
+        <v>0</v>
+      </c>
+      <c r="BF31">
+        <v>0</v>
+      </c>
+      <c r="BG31">
+        <v>0</v>
+      </c>
+      <c r="BH31">
+        <v>0</v>
+      </c>
+      <c r="BI31">
+        <v>0</v>
+      </c>
+      <c r="BJ31">
+        <v>0</v>
+      </c>
+      <c r="BK31">
+        <v>0</v>
+      </c>
+      <c r="BL31">
+        <v>0</v>
+      </c>
+      <c r="BM31">
+        <v>0</v>
+      </c>
+      <c r="BN31">
+        <v>0</v>
+      </c>
+      <c r="BO31">
+        <v>0</v>
+      </c>
+      <c r="BP31">
+        <v>0</v>
+      </c>
+      <c r="BQ31">
+        <v>0</v>
+      </c>
+      <c r="BR31">
+        <v>0</v>
+      </c>
+      <c r="BS31">
+        <v>0</v>
+      </c>
+      <c r="BT31">
+        <v>0</v>
+      </c>
+      <c r="BU31">
+        <v>0</v>
+      </c>
+      <c r="BV31">
+        <v>0</v>
+      </c>
+      <c r="BW31">
+        <v>0</v>
+      </c>
+      <c r="BX31">
+        <v>0</v>
+      </c>
+      <c r="BY31">
+        <v>0</v>
+      </c>
+      <c r="BZ31">
+        <v>0</v>
+      </c>
+      <c r="CA31">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" t="s">
+        <v>153</v>
+      </c>
+      <c r="E32" t="s">
+        <v>191</v>
+      </c>
+      <c r="F32">
+        <v>1.01</v>
+      </c>
+      <c r="G32">
+        <v>1000</v>
+      </c>
+      <c r="H32">
+        <v>1.01</v>
+      </c>
+      <c r="I32">
+        <v>1000</v>
+      </c>
+      <c r="J32">
+        <v>1.01</v>
+      </c>
+      <c r="K32">
         <v>950</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
         <v>1.07</v>
       </c>
-      <c r="Q25">
-        <v>1.01</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>0</v>
-      </c>
-      <c r="BC25">
-        <v>0</v>
-      </c>
-      <c r="BD25">
-        <v>0</v>
-      </c>
-      <c r="BE25">
-        <v>0</v>
-      </c>
-      <c r="BF25">
-        <v>0</v>
-      </c>
-      <c r="BG25">
-        <v>0</v>
-      </c>
-      <c r="BH25">
-        <v>0</v>
-      </c>
-      <c r="BI25">
-        <v>0</v>
-      </c>
-      <c r="BJ25">
-        <v>0</v>
-      </c>
-      <c r="BK25">
-        <v>0</v>
-      </c>
-      <c r="BL25">
-        <v>0</v>
-      </c>
-      <c r="BM25">
-        <v>0</v>
-      </c>
-      <c r="BN25">
-        <v>0</v>
-      </c>
-      <c r="BO25">
-        <v>0</v>
-      </c>
-      <c r="BP25">
-        <v>0</v>
-      </c>
-      <c r="BQ25">
-        <v>0</v>
-      </c>
-      <c r="BR25">
-        <v>0</v>
-      </c>
-      <c r="BS25">
-        <v>0</v>
-      </c>
-      <c r="BT25">
-        <v>0</v>
-      </c>
-      <c r="BU25">
-        <v>0</v>
-      </c>
-      <c r="BV25">
-        <v>0</v>
-      </c>
-      <c r="BW25">
-        <v>0</v>
-      </c>
-      <c r="BX25">
-        <v>0</v>
-      </c>
-      <c r="BY25">
-        <v>0</v>
-      </c>
-      <c r="BZ25">
-        <v>0</v>
-      </c>
-      <c r="CA25">
-        <v>0</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>164</v>
+      <c r="Q32">
+        <v>1.01</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" t="s">
+        <v>154</v>
+      </c>
+      <c r="E33" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33">
+        <v>1.01</v>
+      </c>
+      <c r="G33">
+        <v>1000</v>
+      </c>
+      <c r="H33">
+        <v>1.01</v>
+      </c>
+      <c r="I33">
+        <v>1000</v>
+      </c>
+      <c r="J33">
+        <v>1.01</v>
+      </c>
+      <c r="K33">
+        <v>950</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>1.07</v>
+      </c>
+      <c r="Q33">
+        <v>1.01</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>0</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>0</v>
+      </c>
+      <c r="AV33">
+        <v>0</v>
+      </c>
+      <c r="AW33">
+        <v>0</v>
+      </c>
+      <c r="AX33">
+        <v>0</v>
+      </c>
+      <c r="AY33">
+        <v>0</v>
+      </c>
+      <c r="AZ33">
+        <v>0</v>
+      </c>
+      <c r="BA33">
+        <v>0</v>
+      </c>
+      <c r="BB33">
+        <v>0</v>
+      </c>
+      <c r="BC33">
+        <v>0</v>
+      </c>
+      <c r="BD33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
+        <v>0</v>
+      </c>
+      <c r="BF33">
+        <v>0</v>
+      </c>
+      <c r="BG33">
+        <v>0</v>
+      </c>
+      <c r="BH33">
+        <v>0</v>
+      </c>
+      <c r="BI33">
+        <v>0</v>
+      </c>
+      <c r="BJ33">
+        <v>0</v>
+      </c>
+      <c r="BK33">
+        <v>0</v>
+      </c>
+      <c r="BL33">
+        <v>0</v>
+      </c>
+      <c r="BM33">
+        <v>0</v>
+      </c>
+      <c r="BN33">
+        <v>0</v>
+      </c>
+      <c r="BO33">
+        <v>0</v>
+      </c>
+      <c r="BP33">
+        <v>0</v>
+      </c>
+      <c r="BQ33">
+        <v>0</v>
+      </c>
+      <c r="BR33">
+        <v>0</v>
+      </c>
+      <c r="BS33">
+        <v>0</v>
+      </c>
+      <c r="BT33">
+        <v>0</v>
+      </c>
+      <c r="BU33">
+        <v>0</v>
+      </c>
+      <c r="BV33">
+        <v>0</v>
+      </c>
+      <c r="BW33">
+        <v>0</v>
+      </c>
+      <c r="BX33">
+        <v>0</v>
+      </c>
+      <c r="BY33">
+        <v>0</v>
+      </c>
+      <c r="BZ33">
+        <v>0</v>
+      </c>
+      <c r="CA33">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34">
+        <v>1.17</v>
+      </c>
+      <c r="G34">
+        <v>1.18</v>
+      </c>
+      <c r="H34">
+        <v>21</v>
+      </c>
+      <c r="I34">
+        <v>27</v>
+      </c>
+      <c r="J34">
+        <v>9.4</v>
+      </c>
+      <c r="K34">
+        <v>10.5</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>3.8</v>
+      </c>
+      <c r="Q34">
+        <v>1.32</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="AV34">
+        <v>0</v>
+      </c>
+      <c r="AW34">
+        <v>0</v>
+      </c>
+      <c r="AX34">
+        <v>0</v>
+      </c>
+      <c r="AY34">
+        <v>0</v>
+      </c>
+      <c r="AZ34">
+        <v>0</v>
+      </c>
+      <c r="BA34">
+        <v>0</v>
+      </c>
+      <c r="BB34">
+        <v>0</v>
+      </c>
+      <c r="BC34">
+        <v>0</v>
+      </c>
+      <c r="BD34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="BF34">
+        <v>0</v>
+      </c>
+      <c r="BG34">
+        <v>0</v>
+      </c>
+      <c r="BH34">
+        <v>0</v>
+      </c>
+      <c r="BI34">
+        <v>0</v>
+      </c>
+      <c r="BJ34">
+        <v>0</v>
+      </c>
+      <c r="BK34">
+        <v>0</v>
+      </c>
+      <c r="BL34">
+        <v>0</v>
+      </c>
+      <c r="BM34">
+        <v>0</v>
+      </c>
+      <c r="BN34">
+        <v>0</v>
+      </c>
+      <c r="BO34">
+        <v>0</v>
+      </c>
+      <c r="BP34">
+        <v>0</v>
+      </c>
+      <c r="BQ34">
+        <v>0</v>
+      </c>
+      <c r="BR34">
+        <v>0</v>
+      </c>
+      <c r="BS34">
+        <v>0</v>
+      </c>
+      <c r="BT34">
+        <v>0</v>
+      </c>
+      <c r="BU34">
+        <v>0</v>
+      </c>
+      <c r="BV34">
+        <v>0</v>
+      </c>
+      <c r="BW34">
+        <v>0</v>
+      </c>
+      <c r="BX34">
+        <v>0</v>
+      </c>
+      <c r="BY34">
+        <v>0</v>
+      </c>
+      <c r="BZ34">
+        <v>0</v>
+      </c>
+      <c r="CA34">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" t="s">
+        <v>194</v>
+      </c>
+      <c r="F35">
+        <v>6</v>
+      </c>
+      <c r="G35">
+        <v>7.2</v>
+      </c>
+      <c r="H35">
+        <v>1.6</v>
+      </c>
+      <c r="I35">
+        <v>1.71</v>
+      </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
+      <c r="K35">
+        <v>4.4</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>1.95</v>
+      </c>
+      <c r="Q35">
+        <v>1.87</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>0</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>0</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>0</v>
+      </c>
+      <c r="AV35">
+        <v>0</v>
+      </c>
+      <c r="AW35">
+        <v>0</v>
+      </c>
+      <c r="AX35">
+        <v>0</v>
+      </c>
+      <c r="AY35">
+        <v>0</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
+        <v>0</v>
+      </c>
+      <c r="BC35">
+        <v>0</v>
+      </c>
+      <c r="BD35">
+        <v>0</v>
+      </c>
+      <c r="BE35">
+        <v>0</v>
+      </c>
+      <c r="BF35">
+        <v>0</v>
+      </c>
+      <c r="BG35">
+        <v>0</v>
+      </c>
+      <c r="BH35">
+        <v>0</v>
+      </c>
+      <c r="BI35">
+        <v>0</v>
+      </c>
+      <c r="BJ35">
+        <v>0</v>
+      </c>
+      <c r="BK35">
+        <v>0</v>
+      </c>
+      <c r="BL35">
+        <v>0</v>
+      </c>
+      <c r="BM35">
+        <v>0</v>
+      </c>
+      <c r="BN35">
+        <v>0</v>
+      </c>
+      <c r="BO35">
+        <v>0</v>
+      </c>
+      <c r="BP35">
+        <v>0</v>
+      </c>
+      <c r="BQ35">
+        <v>0</v>
+      </c>
+      <c r="BR35">
+        <v>0</v>
+      </c>
+      <c r="BS35">
+        <v>0</v>
+      </c>
+      <c r="BT35">
+        <v>0</v>
+      </c>
+      <c r="BU35">
+        <v>0</v>
+      </c>
+      <c r="BV35">
+        <v>0</v>
+      </c>
+      <c r="BW35">
+        <v>0</v>
+      </c>
+      <c r="BX35">
+        <v>0</v>
+      </c>
+      <c r="BY35">
+        <v>0</v>
+      </c>
+      <c r="BZ35">
+        <v>0</v>
+      </c>
+      <c r="CA35">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" t="s">
+        <v>195</v>
+      </c>
+      <c r="F36">
+        <v>1.3</v>
+      </c>
+      <c r="G36">
+        <v>1.36</v>
+      </c>
+      <c r="H36">
+        <v>10.5</v>
+      </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
+      <c r="J36">
+        <v>5.6</v>
+      </c>
+      <c r="K36">
+        <v>6.8</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>2.38</v>
+      </c>
+      <c r="Q36">
+        <v>1.56</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>0</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>0</v>
+      </c>
+      <c r="AV36">
+        <v>0</v>
+      </c>
+      <c r="AW36">
+        <v>0</v>
+      </c>
+      <c r="AX36">
+        <v>0</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>0</v>
+      </c>
+      <c r="BA36">
+        <v>0</v>
+      </c>
+      <c r="BB36">
+        <v>0</v>
+      </c>
+      <c r="BC36">
+        <v>0</v>
+      </c>
+      <c r="BD36">
+        <v>0</v>
+      </c>
+      <c r="BE36">
+        <v>0</v>
+      </c>
+      <c r="BF36">
+        <v>0</v>
+      </c>
+      <c r="BG36">
+        <v>0</v>
+      </c>
+      <c r="BH36">
+        <v>0</v>
+      </c>
+      <c r="BI36">
+        <v>0</v>
+      </c>
+      <c r="BJ36">
+        <v>0</v>
+      </c>
+      <c r="BK36">
+        <v>0</v>
+      </c>
+      <c r="BL36">
+        <v>0</v>
+      </c>
+      <c r="BM36">
+        <v>0</v>
+      </c>
+      <c r="BN36">
+        <v>0</v>
+      </c>
+      <c r="BO36">
+        <v>0</v>
+      </c>
+      <c r="BP36">
+        <v>0</v>
+      </c>
+      <c r="BQ36">
+        <v>0</v>
+      </c>
+      <c r="BR36">
+        <v>0</v>
+      </c>
+      <c r="BS36">
+        <v>0</v>
+      </c>
+      <c r="BT36">
+        <v>0</v>
+      </c>
+      <c r="BU36">
+        <v>0</v>
+      </c>
+      <c r="BV36">
+        <v>0</v>
+      </c>
+      <c r="BW36">
+        <v>0</v>
+      </c>
+      <c r="BX36">
+        <v>0</v>
+      </c>
+      <c r="BY36">
+        <v>0</v>
+      </c>
+      <c r="BZ36">
+        <v>0</v>
+      </c>
+      <c r="CA36">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" t="s">
+        <v>158</v>
+      </c>
+      <c r="E37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37">
+        <v>2.3</v>
+      </c>
+      <c r="G37">
+        <v>2.48</v>
+      </c>
+      <c r="H37">
+        <v>2.88</v>
+      </c>
+      <c r="I37">
+        <v>3.15</v>
+      </c>
+      <c r="J37">
+        <v>3.85</v>
+      </c>
+      <c r="K37">
+        <v>4.2</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>2.44</v>
+      </c>
+      <c r="Q37">
+        <v>1.59</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>0</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>0</v>
+      </c>
+      <c r="AV37">
+        <v>0</v>
+      </c>
+      <c r="AW37">
+        <v>0</v>
+      </c>
+      <c r="AX37">
+        <v>0</v>
+      </c>
+      <c r="AY37">
+        <v>0</v>
+      </c>
+      <c r="AZ37">
+        <v>0</v>
+      </c>
+      <c r="BA37">
+        <v>0</v>
+      </c>
+      <c r="BB37">
+        <v>0</v>
+      </c>
+      <c r="BC37">
+        <v>0</v>
+      </c>
+      <c r="BD37">
+        <v>0</v>
+      </c>
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37">
+        <v>0</v>
+      </c>
+      <c r="BG37">
+        <v>0</v>
+      </c>
+      <c r="BH37">
+        <v>0</v>
+      </c>
+      <c r="BI37">
+        <v>0</v>
+      </c>
+      <c r="BJ37">
+        <v>0</v>
+      </c>
+      <c r="BK37">
+        <v>0</v>
+      </c>
+      <c r="BL37">
+        <v>0</v>
+      </c>
+      <c r="BM37">
+        <v>0</v>
+      </c>
+      <c r="BN37">
+        <v>0</v>
+      </c>
+      <c r="BO37">
+        <v>0</v>
+      </c>
+      <c r="BP37">
+        <v>0</v>
+      </c>
+      <c r="BQ37">
+        <v>0</v>
+      </c>
+      <c r="BR37">
+        <v>0</v>
+      </c>
+      <c r="BS37">
+        <v>0</v>
+      </c>
+      <c r="BT37">
+        <v>0</v>
+      </c>
+      <c r="BU37">
+        <v>0</v>
+      </c>
+      <c r="BV37">
+        <v>0</v>
+      </c>
+      <c r="BW37">
+        <v>0</v>
+      </c>
+      <c r="BX37">
+        <v>0</v>
+      </c>
+      <c r="BY37">
+        <v>0</v>
+      </c>
+      <c r="BZ37">
+        <v>0</v>
+      </c>
+      <c r="CA37">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80">
+      <c r="A38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38">
+        <v>1.63</v>
+      </c>
+      <c r="G38">
+        <v>1.65</v>
+      </c>
+      <c r="H38">
+        <v>5.8</v>
+      </c>
+      <c r="I38">
+        <v>6.2</v>
+      </c>
+      <c r="J38">
+        <v>4.4</v>
+      </c>
+      <c r="K38">
+        <v>4.6</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>1.05</v>
+      </c>
+      <c r="N38">
+        <v>5</v>
+      </c>
+      <c r="O38">
+        <v>1.23</v>
+      </c>
+      <c r="P38">
+        <v>2.38</v>
+      </c>
+      <c r="Q38">
+        <v>1.67</v>
+      </c>
+      <c r="R38">
+        <v>1.54</v>
+      </c>
+      <c r="S38">
+        <v>2.7</v>
+      </c>
+      <c r="T38">
+        <v>1.76</v>
+      </c>
+      <c r="U38">
+        <v>2.22</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>22</v>
+      </c>
+      <c r="Y38">
+        <v>26</v>
+      </c>
+      <c r="Z38">
+        <v>60</v>
+      </c>
+      <c r="AA38">
+        <v>1000</v>
+      </c>
+      <c r="AB38">
+        <v>10.5</v>
+      </c>
+      <c r="AC38">
+        <v>10.5</v>
+      </c>
+      <c r="AD38">
+        <v>23</v>
+      </c>
+      <c r="AE38">
+        <v>1000</v>
+      </c>
+      <c r="AF38">
+        <v>11</v>
+      </c>
+      <c r="AG38">
+        <v>10</v>
+      </c>
+      <c r="AH38">
+        <v>20</v>
+      </c>
+      <c r="AI38">
+        <v>1000</v>
+      </c>
+      <c r="AJ38">
+        <v>16.5</v>
+      </c>
+      <c r="AK38">
+        <v>16</v>
+      </c>
+      <c r="AL38">
+        <v>50</v>
+      </c>
+      <c r="AM38">
+        <v>1000</v>
+      </c>
+      <c r="AN38">
+        <v>7.6</v>
+      </c>
+      <c r="AO38">
+        <v>1000</v>
+      </c>
+      <c r="AP38">
+        <v>17.5</v>
+      </c>
+      <c r="AQ38">
+        <v>20</v>
+      </c>
+      <c r="AR38">
+        <v>26</v>
+      </c>
+      <c r="AS38">
+        <v>42</v>
+      </c>
+      <c r="AT38">
+        <v>9.6</v>
+      </c>
+      <c r="AU38">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV38">
+        <v>16</v>
+      </c>
+      <c r="AW38">
+        <v>32</v>
+      </c>
+      <c r="AX38">
+        <v>10</v>
+      </c>
+      <c r="AY38">
+        <v>9</v>
+      </c>
+      <c r="AZ38">
+        <v>16.5</v>
+      </c>
+      <c r="BA38">
+        <v>32</v>
+      </c>
+      <c r="BB38">
+        <v>14</v>
+      </c>
+      <c r="BC38">
+        <v>13.5</v>
+      </c>
+      <c r="BD38">
+        <v>19.5</v>
+      </c>
+      <c r="BE38">
+        <v>36</v>
+      </c>
+      <c r="BF38">
+        <v>6.8</v>
+      </c>
+      <c r="BG38">
+        <v>32</v>
+      </c>
+      <c r="BH38">
+        <v>4.1</v>
+      </c>
+      <c r="BI38">
+        <v>3.7</v>
+      </c>
+      <c r="BJ38">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK38">
+        <v>6.2</v>
+      </c>
+      <c r="BL38">
+        <v>1000</v>
+      </c>
+      <c r="BM38">
+        <v>13.5</v>
+      </c>
+      <c r="BN38">
+        <v>4.4</v>
+      </c>
+      <c r="BO38">
+        <v>4</v>
+      </c>
+      <c r="BP38">
+        <v>10.5</v>
+      </c>
+      <c r="BQ38">
+        <v>6.4</v>
+      </c>
+      <c r="BR38">
+        <v>23</v>
+      </c>
+      <c r="BS38">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT38">
+        <v>9.4</v>
+      </c>
+      <c r="BU38">
+        <v>6</v>
+      </c>
+      <c r="BV38">
+        <v>1000</v>
+      </c>
+      <c r="BW38">
+        <v>11.5</v>
+      </c>
+      <c r="BX38">
+        <v>1000</v>
+      </c>
+      <c r="BY38">
+        <v>11.5</v>
+      </c>
+      <c r="BZ38">
+        <v>15.5</v>
+      </c>
+      <c r="CA38">
+        <v>7.8</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:80">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" t="s">
+        <v>198</v>
+      </c>
+      <c r="F39">
+        <v>1.01</v>
+      </c>
+      <c r="G39">
+        <v>1000</v>
+      </c>
+      <c r="H39">
+        <v>1.01</v>
+      </c>
+      <c r="I39">
+        <v>1000</v>
+      </c>
+      <c r="J39">
+        <v>1.01</v>
+      </c>
+      <c r="K39">
+        <v>950</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>1.07</v>
+      </c>
+      <c r="Q39">
+        <v>1.01</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
+        <v>0</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>0</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39">
+        <v>0</v>
+      </c>
+      <c r="AV39">
+        <v>0</v>
+      </c>
+      <c r="AW39">
+        <v>0</v>
+      </c>
+      <c r="AX39">
+        <v>0</v>
+      </c>
+      <c r="AY39">
+        <v>0</v>
+      </c>
+      <c r="AZ39">
+        <v>0</v>
+      </c>
+      <c r="BA39">
+        <v>0</v>
+      </c>
+      <c r="BB39">
+        <v>0</v>
+      </c>
+      <c r="BC39">
+        <v>0</v>
+      </c>
+      <c r="BD39">
+        <v>0</v>
+      </c>
+      <c r="BE39">
+        <v>0</v>
+      </c>
+      <c r="BF39">
+        <v>0</v>
+      </c>
+      <c r="BG39">
+        <v>0</v>
+      </c>
+      <c r="BH39">
+        <v>0</v>
+      </c>
+      <c r="BI39">
+        <v>0</v>
+      </c>
+      <c r="BJ39">
+        <v>0</v>
+      </c>
+      <c r="BK39">
+        <v>0</v>
+      </c>
+      <c r="BL39">
+        <v>0</v>
+      </c>
+      <c r="BM39">
+        <v>0</v>
+      </c>
+      <c r="BN39">
+        <v>0</v>
+      </c>
+      <c r="BO39">
+        <v>0</v>
+      </c>
+      <c r="BP39">
+        <v>0</v>
+      </c>
+      <c r="BQ39">
+        <v>0</v>
+      </c>
+      <c r="BR39">
+        <v>0</v>
+      </c>
+      <c r="BS39">
+        <v>0</v>
+      </c>
+      <c r="BT39">
+        <v>0</v>
+      </c>
+      <c r="BU39">
+        <v>0</v>
+      </c>
+      <c r="BV39">
+        <v>0</v>
+      </c>
+      <c r="BW39">
+        <v>0</v>
+      </c>
+      <c r="BX39">
+        <v>0</v>
+      </c>
+      <c r="BY39">
+        <v>0</v>
+      </c>
+      <c r="BZ39">
+        <v>0</v>
+      </c>
+      <c r="CA39">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
